--- a/data/2025 SLA Report Spreadsheet.xlsx
+++ b/data/2025 SLA Report Spreadsheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://semtechcorp.sharepoint.com/sites/SierraIntranet/Network-Engineering/Shared Documents/Operations/SLA/.SLA Spreadsheet/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Semtech\TicketDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D26966FB-A11C-4596-8F57-F5A2F28032B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59C1277C-E6F7-438B-9979-3BA75D589376}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="2" xr2:uid="{3BB88C70-2A13-49FB-9ED9-EE67053606B5}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" firstSheet="1" activeTab="1" xr2:uid="{3BB88C70-2A13-49FB-9ED9-EE67053606B5}"/>
   </bookViews>
   <sheets>
     <sheet name="Downtime Entries" sheetId="2" r:id="rId1"/>
@@ -576,7 +576,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2274,18 +2274,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC767CA8-4ECE-4E0B-8A72-B8D62112624D}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:L14"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="0" style="22" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" style="22" customWidth="1"/>
-    <col min="3" max="4" width="65.140625" customWidth="1"/>
-    <col min="5" max="5" width="16.85546875" style="22" customWidth="1"/>
-    <col min="6" max="6" width="8.85546875" style="22"/>
-    <col min="7" max="7" width="18.42578125" style="22" customWidth="1"/>
-    <col min="8" max="8" width="11.5703125" customWidth="1"/>
+    <col min="2" max="2" width="12.54296875" style="22" customWidth="1"/>
+    <col min="3" max="4" width="65.1796875" customWidth="1"/>
+    <col min="5" max="5" width="16.81640625" style="22" customWidth="1"/>
+    <col min="6" max="6" width="8.81640625" style="22"/>
+    <col min="7" max="7" width="18.453125" style="22" customWidth="1"/>
+    <col min="8" max="8" width="11.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
@@ -2311,7 +2311,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="18">
         <v>1</v>
       </c>
@@ -2335,7 +2335,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="18">
         <v>2</v>
       </c>
@@ -2362,7 +2362,7 @@
         <v>4.9800000000000004</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="18">
         <v>3</v>
       </c>
@@ -2389,7 +2389,7 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" s="18">
         <v>4</v>
       </c>
@@ -2416,7 +2416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="18">
         <v>5</v>
       </c>
@@ -2443,7 +2443,7 @@
         <v>3.45</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="18">
         <v>6</v>
       </c>
@@ -2471,7 +2471,7 @@
         <v>10.760000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="18"/>
       <c r="B8" s="20">
         <v>46000</v>
@@ -2493,7 +2493,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="18"/>
       <c r="B9" s="20">
         <v>46003</v>
@@ -2510,10 +2510,10 @@
       </c>
       <c r="H9" s="18"/>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B10" s="23"/>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B13" s="30" t="s">
         <v>1</v>
       </c>
@@ -2536,7 +2536,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B14" s="32">
         <v>46064</v>
       </c>
@@ -2583,7 +2583,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CBCE16C-C45F-4426-85D6-167865B5C26F}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2595,14 +2595,14 @@
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:BO162"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="66" width="11.5703125" style="2"/>
-    <col min="67" max="67" width="11.5703125" style="40"/>
-    <col min="68" max="16384" width="11.5703125" style="2"/>
+    <col min="1" max="66" width="11.54296875" style="2"/>
+    <col min="67" max="67" width="11.54296875" style="40"/>
+    <col min="68" max="16384" width="11.54296875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:67">
+    <row r="1" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A1" s="9" t="s">
         <v>34</v>
       </c>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="BO1" s="39"/>
     </row>
-    <row r="2" spans="1:67">
+    <row r="2" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
         <v>35</v>
       </c>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="BO2" s="39"/>
     </row>
-    <row r="3" spans="1:67">
+    <row r="3" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>36</v>
       </c>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="BO3" s="39"/>
     </row>
-    <row r="4" spans="1:67">
+    <row r="4" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>37</v>
       </c>
@@ -3276,7 +3276,7 @@
       <c r="BN4" s="6"/>
       <c r="BO4" s="39"/>
     </row>
-    <row r="5" spans="1:67">
+    <row r="5" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
         <v>38</v>
       </c>
@@ -3322,7 +3322,9 @@
       <c r="O5" s="4">
         <v>0</v>
       </c>
-      <c r="P5" s="4"/>
+      <c r="P5" s="4">
+        <v>0</v>
+      </c>
       <c r="Q5" s="4"/>
       <c r="R5" s="4"/>
       <c r="S5" s="4"/>
@@ -3375,7 +3377,7 @@
       <c r="BN5" s="4"/>
       <c r="BO5" s="39"/>
     </row>
-    <row r="6" spans="1:67">
+    <row r="6" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
         <v>39</v>
       </c>
@@ -3421,7 +3423,9 @@
       <c r="O6" s="4">
         <v>0</v>
       </c>
-      <c r="P6" s="4"/>
+      <c r="P6" s="4">
+        <v>0</v>
+      </c>
       <c r="Q6" s="4"/>
       <c r="R6" s="4"/>
       <c r="S6" s="4"/>
@@ -3474,7 +3478,7 @@
       <c r="BN6" s="4"/>
       <c r="BO6" s="39"/>
     </row>
-    <row r="7" spans="1:67">
+    <row r="7" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
         <v>40</v>
       </c>
@@ -3520,7 +3524,9 @@
       <c r="O7" s="4">
         <v>0</v>
       </c>
-      <c r="P7" s="4"/>
+      <c r="P7" s="4">
+        <v>0</v>
+      </c>
       <c r="Q7" s="4"/>
       <c r="R7" s="4"/>
       <c r="S7" s="4"/>
@@ -3573,7 +3579,7 @@
       <c r="BN7" s="4"/>
       <c r="BO7" s="39"/>
     </row>
-    <row r="8" spans="1:67">
+    <row r="8" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
         <v>41</v>
       </c>
@@ -3644,7 +3650,7 @@
       <c r="BN8" s="6"/>
       <c r="BO8" s="39"/>
     </row>
-    <row r="9" spans="1:67">
+    <row r="9" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A9" s="8" t="s">
         <v>38</v>
       </c>
@@ -3690,7 +3696,9 @@
       <c r="O9" s="4">
         <v>0</v>
       </c>
-      <c r="P9" s="4"/>
+      <c r="P9" s="4">
+        <v>0</v>
+      </c>
       <c r="Q9" s="4"/>
       <c r="R9" s="4"/>
       <c r="S9" s="4"/>
@@ -3743,7 +3751,7 @@
       <c r="BN9" s="4"/>
       <c r="BO9" s="39"/>
     </row>
-    <row r="10" spans="1:67">
+    <row r="10" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
         <v>39</v>
       </c>
@@ -3789,7 +3797,9 @@
       <c r="O10" s="4">
         <v>0</v>
       </c>
-      <c r="P10" s="4"/>
+      <c r="P10" s="4">
+        <v>0</v>
+      </c>
       <c r="Q10" s="4"/>
       <c r="R10" s="4"/>
       <c r="S10" s="4"/>
@@ -3842,7 +3852,7 @@
       <c r="BN10" s="4"/>
       <c r="BO10" s="39"/>
     </row>
-    <row r="11" spans="1:67">
+    <row r="11" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
         <v>40</v>
       </c>
@@ -3888,7 +3898,9 @@
       <c r="O11" s="4">
         <v>0</v>
       </c>
-      <c r="P11" s="4"/>
+      <c r="P11" s="4">
+        <v>0</v>
+      </c>
       <c r="Q11" s="4"/>
       <c r="R11" s="4"/>
       <c r="S11" s="4"/>
@@ -3941,7 +3953,7 @@
       <c r="BN11" s="4"/>
       <c r="BO11" s="39"/>
     </row>
-    <row r="12" spans="1:67">
+    <row r="12" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
         <v>42</v>
       </c>
@@ -4012,7 +4024,7 @@
       <c r="BN12" s="7"/>
       <c r="BO12" s="39"/>
     </row>
-    <row r="13" spans="1:67">
+    <row r="13" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A13" s="8" t="s">
         <v>38</v>
       </c>
@@ -4058,7 +4070,9 @@
       <c r="O13" s="4">
         <v>0</v>
       </c>
-      <c r="P13" s="4"/>
+      <c r="P13" s="4">
+        <v>0</v>
+      </c>
       <c r="Q13" s="4"/>
       <c r="R13" s="4"/>
       <c r="S13" s="4"/>
@@ -4111,7 +4125,7 @@
       <c r="BN13" s="4"/>
       <c r="BO13" s="39"/>
     </row>
-    <row r="14" spans="1:67">
+    <row r="14" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
         <v>39</v>
       </c>
@@ -4157,7 +4171,9 @@
       <c r="O14" s="4">
         <v>0</v>
       </c>
-      <c r="P14" s="4"/>
+      <c r="P14" s="4">
+        <v>0</v>
+      </c>
       <c r="Q14" s="4"/>
       <c r="R14" s="4"/>
       <c r="S14" s="4"/>
@@ -4210,7 +4226,7 @@
       <c r="BN14" s="4"/>
       <c r="BO14" s="39"/>
     </row>
-    <row r="15" spans="1:67">
+    <row r="15" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A15" s="8" t="s">
         <v>40</v>
       </c>
@@ -4256,7 +4272,9 @@
       <c r="O15" s="4">
         <v>0</v>
       </c>
-      <c r="P15" s="4"/>
+      <c r="P15" s="4">
+        <v>0</v>
+      </c>
       <c r="Q15" s="4"/>
       <c r="R15" s="4"/>
       <c r="S15" s="4"/>
@@ -4309,7 +4327,7 @@
       <c r="BN15" s="4"/>
       <c r="BO15" s="39"/>
     </row>
-    <row r="16" spans="1:67">
+    <row r="16" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
         <v>43</v>
       </c>
@@ -4380,7 +4398,7 @@
       <c r="BN16" s="7"/>
       <c r="BO16" s="39"/>
     </row>
-    <row r="17" spans="1:67">
+    <row r="17" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A17" s="8" t="s">
         <v>38</v>
       </c>
@@ -4426,7 +4444,9 @@
       <c r="O17" s="4">
         <v>0</v>
       </c>
-      <c r="P17" s="4"/>
+      <c r="P17" s="4">
+        <v>0</v>
+      </c>
       <c r="Q17" s="4"/>
       <c r="R17" s="4"/>
       <c r="S17" s="4"/>
@@ -4479,7 +4499,7 @@
       <c r="BN17" s="4"/>
       <c r="BO17" s="39"/>
     </row>
-    <row r="18" spans="1:67">
+    <row r="18" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A18" s="8" t="s">
         <v>39</v>
       </c>
@@ -4525,7 +4545,9 @@
       <c r="O18" s="4">
         <v>0</v>
       </c>
-      <c r="P18" s="4"/>
+      <c r="P18" s="4">
+        <v>0</v>
+      </c>
       <c r="Q18" s="4"/>
       <c r="R18" s="4"/>
       <c r="S18" s="4"/>
@@ -4578,7 +4600,7 @@
       <c r="BN18" s="4"/>
       <c r="BO18" s="39"/>
     </row>
-    <row r="19" spans="1:67">
+    <row r="19" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A19" s="8" t="s">
         <v>40</v>
       </c>
@@ -4624,7 +4646,9 @@
       <c r="O19" s="4">
         <v>0</v>
       </c>
-      <c r="P19" s="4"/>
+      <c r="P19" s="4">
+        <v>0</v>
+      </c>
       <c r="Q19" s="4"/>
       <c r="R19" s="4"/>
       <c r="S19" s="4"/>
@@ -4677,7 +4701,7 @@
       <c r="BN19" s="4"/>
       <c r="BO19" s="39"/>
     </row>
-    <row r="20" spans="1:67">
+    <row r="20" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A20" s="7" t="s">
         <v>44</v>
       </c>
@@ -4748,7 +4772,7 @@
       <c r="BN20" s="7"/>
       <c r="BO20" s="39"/>
     </row>
-    <row r="21" spans="1:67">
+    <row r="21" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A21" s="8" t="s">
         <v>38</v>
       </c>
@@ -4794,7 +4818,9 @@
       <c r="O21" s="4">
         <v>0</v>
       </c>
-      <c r="P21" s="4"/>
+      <c r="P21" s="4">
+        <v>0</v>
+      </c>
       <c r="Q21" s="4"/>
       <c r="R21" s="4"/>
       <c r="S21" s="4"/>
@@ -4847,7 +4873,7 @@
       <c r="BN21" s="4"/>
       <c r="BO21" s="39"/>
     </row>
-    <row r="22" spans="1:67">
+    <row r="22" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
         <v>45</v>
       </c>
@@ -4918,7 +4944,7 @@
       <c r="BN22" s="7"/>
       <c r="BO22" s="39"/>
     </row>
-    <row r="23" spans="1:67">
+    <row r="23" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A23" s="8" t="s">
         <v>38</v>
       </c>
@@ -4964,7 +4990,9 @@
       <c r="O23" s="4">
         <v>0</v>
       </c>
-      <c r="P23" s="4"/>
+      <c r="P23" s="4">
+        <v>0</v>
+      </c>
       <c r="Q23" s="4"/>
       <c r="R23" s="4"/>
       <c r="S23" s="4"/>
@@ -5017,7 +5045,7 @@
       <c r="BN23" s="4"/>
       <c r="BO23" s="39"/>
     </row>
-    <row r="24" spans="1:67">
+    <row r="24" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A24" s="8" t="s">
         <v>39</v>
       </c>
@@ -5063,7 +5091,9 @@
       <c r="O24" s="4">
         <v>0</v>
       </c>
-      <c r="P24" s="4"/>
+      <c r="P24" s="4">
+        <v>0</v>
+      </c>
       <c r="Q24" s="4"/>
       <c r="R24" s="4"/>
       <c r="S24" s="4"/>
@@ -5116,7 +5146,7 @@
       <c r="BN24" s="4"/>
       <c r="BO24" s="39"/>
     </row>
-    <row r="25" spans="1:67">
+    <row r="25" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A25" s="8" t="s">
         <v>40</v>
       </c>
@@ -5162,7 +5192,9 @@
       <c r="O25" s="4">
         <v>0</v>
       </c>
-      <c r="P25" s="4"/>
+      <c r="P25" s="4">
+        <v>0</v>
+      </c>
       <c r="Q25" s="4"/>
       <c r="R25" s="4"/>
       <c r="S25" s="4"/>
@@ -5215,7 +5247,7 @@
       <c r="BN25" s="4"/>
       <c r="BO25" s="39"/>
     </row>
-    <row r="26" spans="1:67">
+    <row r="26" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A26" s="6"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -5284,13 +5316,13 @@
       <c r="BN26" s="6"/>
       <c r="BO26" s="39"/>
     </row>
-    <row r="27" spans="1:67">
+    <row r="27" spans="1:67" x14ac:dyDescent="0.35">
       <c r="BO27" s="39"/>
     </row>
-    <row r="28" spans="1:67">
+    <row r="28" spans="1:67" x14ac:dyDescent="0.35">
       <c r="BO28" s="39"/>
     </row>
-    <row r="29" spans="1:67">
+    <row r="29" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A29" s="7" t="s">
         <v>46</v>
       </c>
@@ -5361,7 +5393,7 @@
       <c r="BN29" s="6"/>
       <c r="BO29" s="39"/>
     </row>
-    <row r="30" spans="1:67" hidden="1">
+    <row r="30" spans="1:67" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="7" t="s">
         <v>47</v>
       </c>
@@ -5440,7 +5472,7 @@
       <c r="BN30" s="10"/>
       <c r="BO30" s="39"/>
     </row>
-    <row r="31" spans="1:67" hidden="1">
+    <row r="31" spans="1:67" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="8" t="s">
         <v>38</v>
       </c>
@@ -5511,7 +5543,7 @@
       <c r="BN31" s="29"/>
       <c r="BO31" s="39"/>
     </row>
-    <row r="32" spans="1:67" hidden="1">
+    <row r="32" spans="1:67" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="8" t="s">
         <v>39</v>
       </c>
@@ -5582,7 +5614,7 @@
       <c r="BN32" s="29"/>
       <c r="BO32" s="39"/>
     </row>
-    <row r="33" spans="1:67" hidden="1">
+    <row r="33" spans="1:67" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="8" t="s">
         <v>40</v>
       </c>
@@ -5653,7 +5685,7 @@
       <c r="BN33" s="29"/>
       <c r="BO33" s="39"/>
     </row>
-    <row r="34" spans="1:67">
+    <row r="34" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A34" s="7" t="s">
         <v>37</v>
       </c>
@@ -5724,7 +5756,7 @@
       <c r="BN34" s="6"/>
       <c r="BO34" s="39"/>
     </row>
-    <row r="35" spans="1:67">
+    <row r="35" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A35" s="8" t="s">
         <v>38</v>
       </c>
@@ -5785,7 +5817,7 @@
         <v>1</v>
       </c>
       <c r="P35" s="5">
-        <f t="shared" ref="O35:AF35" si="4">1-(P5/P1)</f>
+        <f t="shared" ref="P35:AF35" si="4">1-(P5/P1)</f>
         <v>1</v>
       </c>
       <c r="Q35" s="5">
@@ -5990,7 +6022,7 @@
       </c>
       <c r="BO35" s="39"/>
     </row>
-    <row r="36" spans="1:67">
+    <row r="36" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A36" s="8" t="s">
         <v>39</v>
       </c>
@@ -6051,7 +6083,7 @@
         <v>1</v>
       </c>
       <c r="P36" s="5">
-        <f t="shared" ref="O36:AF36" si="10">1-(P6/P1)</f>
+        <f t="shared" ref="P36:AF36" si="10">1-(P6/P1)</f>
         <v>1</v>
       </c>
       <c r="Q36" s="5">
@@ -6256,7 +6288,7 @@
       </c>
       <c r="BO36" s="39"/>
     </row>
-    <row r="37" spans="1:67">
+    <row r="37" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A37" s="8" t="s">
         <v>40</v>
       </c>
@@ -6317,7 +6349,7 @@
         <v>1</v>
       </c>
       <c r="P37" s="5">
-        <f t="shared" ref="O37:AF37" si="16">1-(P7/P1)</f>
+        <f t="shared" ref="P37:AF37" si="16">1-(P7/P1)</f>
         <v>1</v>
       </c>
       <c r="Q37" s="5">
@@ -6522,7 +6554,7 @@
       </c>
       <c r="BO37" s="39"/>
     </row>
-    <row r="38" spans="1:67">
+    <row r="38" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A38" s="7" t="s">
         <v>41</v>
       </c>
@@ -6593,7 +6625,7 @@
       <c r="BN38" s="6"/>
       <c r="BO38" s="39"/>
     </row>
-    <row r="39" spans="1:67">
+    <row r="39" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A39" s="8" t="s">
         <v>38</v>
       </c>
@@ -6654,7 +6686,7 @@
         <v>1</v>
       </c>
       <c r="P39" s="5">
-        <f t="shared" ref="O39:AF39" si="22">1-(P9/P1)</f>
+        <f t="shared" ref="P39:AF39" si="22">1-(P9/P1)</f>
         <v>1</v>
       </c>
       <c r="Q39" s="5">
@@ -6859,7 +6891,7 @@
       </c>
       <c r="BO39" s="39"/>
     </row>
-    <row r="40" spans="1:67">
+    <row r="40" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A40" s="8" t="s">
         <v>39</v>
       </c>
@@ -6920,7 +6952,7 @@
         <v>1</v>
       </c>
       <c r="P40" s="5">
-        <f t="shared" ref="O40:AF40" si="28">1-(P10/P1)</f>
+        <f t="shared" ref="P40:AF40" si="28">1-(P10/P1)</f>
         <v>1</v>
       </c>
       <c r="Q40" s="5">
@@ -7125,7 +7157,7 @@
       </c>
       <c r="BO40" s="39"/>
     </row>
-    <row r="41" spans="1:67">
+    <row r="41" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A41" s="8" t="s">
         <v>40</v>
       </c>
@@ -7186,7 +7218,7 @@
         <v>1</v>
       </c>
       <c r="P41" s="5">
-        <f t="shared" ref="O41:AF41" si="34">1-(P11/P1)</f>
+        <f t="shared" ref="P41:AF41" si="34">1-(P11/P1)</f>
         <v>1</v>
       </c>
       <c r="Q41" s="5">
@@ -7391,7 +7423,7 @@
       </c>
       <c r="BO41" s="39"/>
     </row>
-    <row r="42" spans="1:67">
+    <row r="42" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A42" s="7" t="s">
         <v>42</v>
       </c>
@@ -7462,7 +7494,7 @@
       <c r="BN42" s="6"/>
       <c r="BO42" s="39"/>
     </row>
-    <row r="43" spans="1:67">
+    <row r="43" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A43" s="8" t="s">
         <v>38</v>
       </c>
@@ -7523,7 +7555,7 @@
         <v>1</v>
       </c>
       <c r="P43" s="5">
-        <f t="shared" ref="O43:AF43" si="40">1-(P13/P1)</f>
+        <f t="shared" ref="P43:AF43" si="40">1-(P13/P1)</f>
         <v>1</v>
       </c>
       <c r="Q43" s="5">
@@ -7728,7 +7760,7 @@
       </c>
       <c r="BO43" s="39"/>
     </row>
-    <row r="44" spans="1:67">
+    <row r="44" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A44" s="8" t="s">
         <v>39</v>
       </c>
@@ -7789,7 +7821,7 @@
         <v>1</v>
       </c>
       <c r="P44" s="5">
-        <f t="shared" ref="O44:AF44" si="46">1-(P14/P1)</f>
+        <f t="shared" ref="P44:AF44" si="46">1-(P14/P1)</f>
         <v>1</v>
       </c>
       <c r="Q44" s="5">
@@ -7994,7 +8026,7 @@
       </c>
       <c r="BO44" s="39"/>
     </row>
-    <row r="45" spans="1:67">
+    <row r="45" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A45" s="8" t="s">
         <v>40</v>
       </c>
@@ -8055,7 +8087,7 @@
         <v>1</v>
       </c>
       <c r="P45" s="5">
-        <f t="shared" ref="O45:AF45" si="52">1-(P15/P1)</f>
+        <f t="shared" ref="P45:AF45" si="52">1-(P15/P1)</f>
         <v>1</v>
       </c>
       <c r="Q45" s="5">
@@ -8260,7 +8292,7 @@
       </c>
       <c r="BO45" s="39"/>
     </row>
-    <row r="46" spans="1:67">
+    <row r="46" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A46" s="7" t="s">
         <v>43</v>
       </c>
@@ -8331,7 +8363,7 @@
       <c r="BN46" s="6"/>
       <c r="BO46" s="39"/>
     </row>
-    <row r="47" spans="1:67">
+    <row r="47" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A47" s="8" t="s">
         <v>38</v>
       </c>
@@ -8392,7 +8424,7 @@
         <v>1</v>
       </c>
       <c r="P47" s="5">
-        <f t="shared" ref="O47:AF47" si="58">1-(P17/P1)</f>
+        <f t="shared" ref="P47:AF47" si="58">1-(P17/P1)</f>
         <v>1</v>
       </c>
       <c r="Q47" s="5">
@@ -8597,7 +8629,7 @@
       </c>
       <c r="BO47" s="39"/>
     </row>
-    <row r="48" spans="1:67">
+    <row r="48" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A48" s="8" t="s">
         <v>39</v>
       </c>
@@ -8658,7 +8690,7 @@
         <v>1</v>
       </c>
       <c r="P48" s="5">
-        <f t="shared" ref="O48:AF48" si="64">1-(P18/P1)</f>
+        <f t="shared" ref="P48:AF48" si="64">1-(P18/P1)</f>
         <v>1</v>
       </c>
       <c r="Q48" s="5">
@@ -8863,7 +8895,7 @@
       </c>
       <c r="BO48" s="39"/>
     </row>
-    <row r="49" spans="1:67">
+    <row r="49" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A49" s="8" t="s">
         <v>40</v>
       </c>
@@ -8924,7 +8956,7 @@
         <v>1</v>
       </c>
       <c r="P49" s="5">
-        <f t="shared" ref="O49:AF49" si="70">1-(P19/P1)</f>
+        <f t="shared" ref="P49:AF49" si="70">1-(P19/P1)</f>
         <v>1</v>
       </c>
       <c r="Q49" s="5">
@@ -9129,7 +9161,7 @@
       </c>
       <c r="BO49" s="39"/>
     </row>
-    <row r="50" spans="1:67">
+    <row r="50" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A50" s="7" t="s">
         <v>44</v>
       </c>
@@ -9200,7 +9232,7 @@
       <c r="BN50" s="6"/>
       <c r="BO50" s="39"/>
     </row>
-    <row r="51" spans="1:67">
+    <row r="51" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A51" s="8" t="s">
         <v>38</v>
       </c>
@@ -9261,7 +9293,7 @@
         <v>1</v>
       </c>
       <c r="P51" s="5">
-        <f t="shared" ref="O51:AF51" si="76">1-(P21/P1)</f>
+        <f t="shared" ref="P51:AF51" si="76">1-(P21/P1)</f>
         <v>1</v>
       </c>
       <c r="Q51" s="5">
@@ -9466,7 +9498,7 @@
       </c>
       <c r="BO51" s="39"/>
     </row>
-    <row r="52" spans="1:67">
+    <row r="52" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A52" s="7" t="s">
         <v>45</v>
       </c>
@@ -9537,7 +9569,7 @@
       <c r="BN52" s="6"/>
       <c r="BO52" s="39"/>
     </row>
-    <row r="53" spans="1:67">
+    <row r="53" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A53" s="8" t="s">
         <v>38</v>
       </c>
@@ -9598,7 +9630,7 @@
         <v>1</v>
       </c>
       <c r="P53" s="5">
-        <f t="shared" ref="O53:AF53" si="82">1-(P23/P1)</f>
+        <f t="shared" ref="P53:AF53" si="82">1-(P23/P1)</f>
         <v>1</v>
       </c>
       <c r="Q53" s="5">
@@ -9803,7 +9835,7 @@
       </c>
       <c r="BO53" s="39"/>
     </row>
-    <row r="54" spans="1:67">
+    <row r="54" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A54" s="8" t="s">
         <v>39</v>
       </c>
@@ -9864,7 +9896,7 @@
         <v>1</v>
       </c>
       <c r="P54" s="5">
-        <f t="shared" ref="O54:AF54" si="88">1-(P24/P1)</f>
+        <f t="shared" ref="P54:AF54" si="88">1-(P24/P1)</f>
         <v>1</v>
       </c>
       <c r="Q54" s="5">
@@ -10069,7 +10101,7 @@
       </c>
       <c r="BO54" s="39"/>
     </row>
-    <row r="55" spans="1:67">
+    <row r="55" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A55" s="8" t="s">
         <v>40</v>
       </c>
@@ -10130,7 +10162,7 @@
         <v>1</v>
       </c>
       <c r="P55" s="5">
-        <f t="shared" ref="O55:AF55" si="94">1-(P25/P1)</f>
+        <f t="shared" ref="P55:AF55" si="94">1-(P25/P1)</f>
         <v>1</v>
       </c>
       <c r="Q55" s="5">
@@ -10335,7 +10367,7 @@
       </c>
       <c r="BO55" s="39"/>
     </row>
-    <row r="56" spans="1:67">
+    <row r="56" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A56" s="6"/>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
@@ -10404,427 +10436,427 @@
       <c r="BN56" s="6"/>
       <c r="BO56" s="39"/>
     </row>
-    <row r="57" spans="1:67">
+    <row r="57" spans="1:67" x14ac:dyDescent="0.35">
       <c r="BN57" s="38"/>
       <c r="BO57" s="39"/>
     </row>
-    <row r="58" spans="1:67">
+    <row r="58" spans="1:67" x14ac:dyDescent="0.35">
       <c r="BN58" s="38"/>
       <c r="BO58" s="39"/>
     </row>
-    <row r="59" spans="1:67">
+    <row r="59" spans="1:67" x14ac:dyDescent="0.35">
       <c r="BN59" s="38"/>
       <c r="BO59" s="39"/>
     </row>
-    <row r="60" spans="1:67">
+    <row r="60" spans="1:67" x14ac:dyDescent="0.35">
       <c r="BN60" s="38"/>
       <c r="BO60" s="39"/>
     </row>
-    <row r="61" spans="1:67">
+    <row r="61" spans="1:67" x14ac:dyDescent="0.35">
       <c r="BN61" s="38"/>
       <c r="BO61" s="39"/>
     </row>
-    <row r="62" spans="1:67">
+    <row r="62" spans="1:67" x14ac:dyDescent="0.35">
       <c r="BN62" s="38"/>
       <c r="BO62" s="39"/>
     </row>
-    <row r="63" spans="1:67">
+    <row r="63" spans="1:67" x14ac:dyDescent="0.35">
       <c r="BN63" s="38"/>
       <c r="BO63" s="39"/>
     </row>
-    <row r="64" spans="1:67">
+    <row r="64" spans="1:67" x14ac:dyDescent="0.35">
       <c r="BN64" s="38"/>
       <c r="BO64" s="39"/>
     </row>
-    <row r="65" spans="66:67">
+    <row r="65" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN65" s="38"/>
       <c r="BO65" s="39"/>
     </row>
-    <row r="66" spans="66:67">
+    <row r="66" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN66" s="38"/>
       <c r="BO66" s="39"/>
     </row>
-    <row r="67" spans="66:67">
+    <row r="67" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN67" s="38"/>
       <c r="BO67" s="39"/>
     </row>
-    <row r="68" spans="66:67">
+    <row r="68" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN68" s="38"/>
       <c r="BO68" s="39"/>
     </row>
-    <row r="69" spans="66:67">
+    <row r="69" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN69" s="38"/>
       <c r="BO69" s="39"/>
     </row>
-    <row r="70" spans="66:67">
+    <row r="70" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN70" s="38"/>
       <c r="BO70" s="39"/>
     </row>
-    <row r="71" spans="66:67">
+    <row r="71" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN71" s="38"/>
       <c r="BO71" s="39"/>
     </row>
-    <row r="72" spans="66:67">
+    <row r="72" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN72" s="38"/>
       <c r="BO72" s="39"/>
     </row>
-    <row r="73" spans="66:67">
+    <row r="73" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN73" s="38"/>
       <c r="BO73" s="39"/>
     </row>
-    <row r="74" spans="66:67">
+    <row r="74" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN74" s="38"/>
       <c r="BO74" s="39"/>
     </row>
-    <row r="75" spans="66:67">
+    <row r="75" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN75" s="38"/>
       <c r="BO75" s="39"/>
     </row>
-    <row r="76" spans="66:67">
+    <row r="76" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN76" s="38"/>
       <c r="BO76" s="39"/>
     </row>
-    <row r="77" spans="66:67">
+    <row r="77" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN77" s="38"/>
       <c r="BO77" s="39"/>
     </row>
-    <row r="78" spans="66:67">
+    <row r="78" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN78" s="38"/>
       <c r="BO78" s="39"/>
     </row>
-    <row r="79" spans="66:67">
+    <row r="79" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN79" s="38"/>
       <c r="BO79" s="39"/>
     </row>
-    <row r="80" spans="66:67">
+    <row r="80" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN80" s="38"/>
       <c r="BO80" s="39"/>
     </row>
-    <row r="81" spans="66:67">
+    <row r="81" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN81" s="38"/>
       <c r="BO81" s="39"/>
     </row>
-    <row r="82" spans="66:67">
+    <row r="82" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN82" s="38"/>
       <c r="BO82" s="39"/>
     </row>
-    <row r="83" spans="66:67">
+    <row r="83" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN83" s="38"/>
       <c r="BO83" s="39"/>
     </row>
-    <row r="84" spans="66:67">
+    <row r="84" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN84" s="38"/>
       <c r="BO84" s="39"/>
     </row>
-    <row r="85" spans="66:67">
+    <row r="85" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN85" s="38"/>
       <c r="BO85" s="39"/>
     </row>
-    <row r="86" spans="66:67">
+    <row r="86" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN86" s="38"/>
       <c r="BO86" s="39"/>
     </row>
-    <row r="87" spans="66:67">
+    <row r="87" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN87" s="38"/>
       <c r="BO87" s="39"/>
     </row>
-    <row r="88" spans="66:67">
+    <row r="88" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN88" s="38"/>
       <c r="BO88" s="39"/>
     </row>
-    <row r="89" spans="66:67">
+    <row r="89" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN89" s="38"/>
       <c r="BO89" s="39"/>
     </row>
-    <row r="90" spans="66:67">
+    <row r="90" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN90" s="38"/>
       <c r="BO90" s="39"/>
     </row>
-    <row r="91" spans="66:67">
+    <row r="91" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN91" s="38"/>
       <c r="BO91" s="39"/>
     </row>
-    <row r="92" spans="66:67">
+    <row r="92" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN92" s="38"/>
       <c r="BO92" s="39"/>
     </row>
-    <row r="93" spans="66:67">
+    <row r="93" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN93" s="38"/>
       <c r="BO93" s="39"/>
     </row>
-    <row r="94" spans="66:67">
+    <row r="94" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN94" s="38"/>
       <c r="BO94" s="39"/>
     </row>
-    <row r="95" spans="66:67">
+    <row r="95" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN95" s="38"/>
       <c r="BO95" s="39"/>
     </row>
-    <row r="96" spans="66:67">
+    <row r="96" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN96" s="38"/>
       <c r="BO96" s="39"/>
     </row>
-    <row r="97" spans="66:67">
+    <row r="97" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN97" s="38"/>
       <c r="BO97" s="39"/>
     </row>
-    <row r="98" spans="66:67">
+    <row r="98" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN98" s="38"/>
       <c r="BO98" s="39"/>
     </row>
-    <row r="99" spans="66:67">
+    <row r="99" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN99" s="38"/>
       <c r="BO99" s="39"/>
     </row>
-    <row r="100" spans="66:67">
+    <row r="100" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN100" s="38"/>
       <c r="BO100" s="39"/>
     </row>
-    <row r="101" spans="66:67">
+    <row r="101" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN101" s="38"/>
       <c r="BO101" s="39"/>
     </row>
-    <row r="102" spans="66:67">
+    <row r="102" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN102" s="38"/>
       <c r="BO102" s="39"/>
     </row>
-    <row r="103" spans="66:67">
+    <row r="103" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN103" s="38"/>
       <c r="BO103" s="39"/>
     </row>
-    <row r="104" spans="66:67">
+    <row r="104" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN104" s="38"/>
       <c r="BO104" s="39"/>
     </row>
-    <row r="105" spans="66:67">
+    <row r="105" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN105" s="38"/>
       <c r="BO105" s="39"/>
     </row>
-    <row r="106" spans="66:67">
+    <row r="106" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN106" s="38"/>
       <c r="BO106" s="39"/>
     </row>
-    <row r="107" spans="66:67">
+    <row r="107" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN107" s="38"/>
       <c r="BO107" s="39"/>
     </row>
-    <row r="108" spans="66:67">
+    <row r="108" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN108" s="38"/>
       <c r="BO108" s="39"/>
     </row>
-    <row r="109" spans="66:67">
+    <row r="109" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN109" s="38"/>
       <c r="BO109" s="39"/>
     </row>
-    <row r="110" spans="66:67">
+    <row r="110" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN110" s="38"/>
       <c r="BO110" s="39"/>
     </row>
-    <row r="111" spans="66:67">
+    <row r="111" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN111" s="38"/>
       <c r="BO111" s="39"/>
     </row>
-    <row r="112" spans="66:67">
+    <row r="112" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN112" s="38"/>
       <c r="BO112" s="39"/>
     </row>
-    <row r="113" spans="66:67">
+    <row r="113" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN113" s="38"/>
       <c r="BO113" s="39"/>
     </row>
-    <row r="114" spans="66:67">
+    <row r="114" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN114" s="38"/>
       <c r="BO114" s="39"/>
     </row>
-    <row r="115" spans="66:67">
+    <row r="115" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN115" s="38"/>
       <c r="BO115" s="39"/>
     </row>
-    <row r="116" spans="66:67">
+    <row r="116" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN116" s="38"/>
       <c r="BO116" s="39"/>
     </row>
-    <row r="117" spans="66:67">
+    <row r="117" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN117" s="38"/>
       <c r="BO117" s="39"/>
     </row>
-    <row r="118" spans="66:67">
+    <row r="118" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN118" s="38"/>
       <c r="BO118" s="39"/>
     </row>
-    <row r="119" spans="66:67">
+    <row r="119" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN119" s="38"/>
       <c r="BO119" s="39"/>
     </row>
-    <row r="120" spans="66:67">
+    <row r="120" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN120" s="38"/>
       <c r="BO120" s="39"/>
     </row>
-    <row r="121" spans="66:67">
+    <row r="121" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN121" s="38"/>
       <c r="BO121" s="39"/>
     </row>
-    <row r="122" spans="66:67">
+    <row r="122" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN122" s="38"/>
       <c r="BO122" s="39"/>
     </row>
-    <row r="123" spans="66:67">
+    <row r="123" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN123" s="38"/>
       <c r="BO123" s="39"/>
     </row>
-    <row r="124" spans="66:67">
+    <row r="124" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN124" s="38"/>
       <c r="BO124" s="39"/>
     </row>
-    <row r="125" spans="66:67">
+    <row r="125" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN125" s="38"/>
       <c r="BO125" s="39"/>
     </row>
-    <row r="126" spans="66:67">
+    <row r="126" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN126" s="38"/>
       <c r="BO126" s="39"/>
     </row>
-    <row r="127" spans="66:67">
+    <row r="127" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN127" s="38"/>
       <c r="BO127" s="39"/>
     </row>
-    <row r="128" spans="66:67">
+    <row r="128" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN128" s="38"/>
       <c r="BO128" s="39"/>
     </row>
-    <row r="129" spans="66:67">
+    <row r="129" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN129" s="38"/>
       <c r="BO129" s="39"/>
     </row>
-    <row r="130" spans="66:67">
+    <row r="130" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN130" s="38"/>
       <c r="BO130" s="39"/>
     </row>
-    <row r="131" spans="66:67">
+    <row r="131" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN131" s="38"/>
       <c r="BO131" s="39"/>
     </row>
-    <row r="132" spans="66:67">
+    <row r="132" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN132" s="38"/>
       <c r="BO132" s="39"/>
     </row>
-    <row r="133" spans="66:67">
+    <row r="133" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN133" s="38"/>
       <c r="BO133" s="39"/>
     </row>
-    <row r="134" spans="66:67">
+    <row r="134" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN134" s="38"/>
       <c r="BO134" s="39"/>
     </row>
-    <row r="135" spans="66:67">
+    <row r="135" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN135" s="38"/>
       <c r="BO135" s="39"/>
     </row>
-    <row r="136" spans="66:67">
+    <row r="136" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN136" s="38"/>
       <c r="BO136" s="39"/>
     </row>
-    <row r="137" spans="66:67">
+    <row r="137" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN137" s="38"/>
       <c r="BO137" s="39"/>
     </row>
-    <row r="138" spans="66:67">
+    <row r="138" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN138" s="38"/>
       <c r="BO138" s="39"/>
     </row>
-    <row r="139" spans="66:67">
+    <row r="139" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN139" s="38"/>
       <c r="BO139" s="39"/>
     </row>
-    <row r="140" spans="66:67">
+    <row r="140" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN140" s="38"/>
       <c r="BO140" s="39"/>
     </row>
-    <row r="141" spans="66:67">
+    <row r="141" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN141" s="38"/>
       <c r="BO141" s="39"/>
     </row>
-    <row r="142" spans="66:67">
+    <row r="142" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN142" s="38"/>
       <c r="BO142" s="39"/>
     </row>
-    <row r="143" spans="66:67">
+    <row r="143" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN143" s="38"/>
       <c r="BO143" s="39"/>
     </row>
-    <row r="144" spans="66:67">
+    <row r="144" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN144" s="38"/>
       <c r="BO144" s="39"/>
     </row>
-    <row r="145" spans="66:67">
+    <row r="145" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN145" s="38"/>
       <c r="BO145" s="39"/>
     </row>
-    <row r="146" spans="66:67">
+    <row r="146" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN146" s="38"/>
       <c r="BO146" s="39"/>
     </row>
-    <row r="147" spans="66:67">
+    <row r="147" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN147" s="38"/>
       <c r="BO147" s="39"/>
     </row>
-    <row r="148" spans="66:67">
+    <row r="148" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN148" s="38"/>
       <c r="BO148" s="39"/>
     </row>
-    <row r="149" spans="66:67">
+    <row r="149" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN149" s="38"/>
       <c r="BO149" s="39"/>
     </row>
-    <row r="150" spans="66:67">
+    <row r="150" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN150" s="38"/>
       <c r="BO150" s="39"/>
     </row>
-    <row r="151" spans="66:67">
+    <row r="151" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN151" s="38"/>
       <c r="BO151" s="39"/>
     </row>
-    <row r="152" spans="66:67">
+    <row r="152" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN152" s="38"/>
       <c r="BO152" s="39"/>
     </row>
-    <row r="153" spans="66:67">
+    <row r="153" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN153" s="38"/>
       <c r="BO153" s="39"/>
     </row>
-    <row r="154" spans="66:67">
+    <row r="154" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN154" s="38"/>
       <c r="BO154" s="39"/>
     </row>
-    <row r="155" spans="66:67">
+    <row r="155" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN155" s="38"/>
       <c r="BO155" s="39"/>
     </row>
-    <row r="156" spans="66:67">
+    <row r="156" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN156" s="38"/>
       <c r="BO156" s="39"/>
     </row>
-    <row r="157" spans="66:67">
+    <row r="157" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN157" s="38"/>
       <c r="BO157" s="39"/>
     </row>
-    <row r="158" spans="66:67">
+    <row r="158" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN158" s="38"/>
       <c r="BO158" s="39"/>
     </row>
-    <row r="159" spans="66:67">
+    <row r="159" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN159" s="38"/>
       <c r="BO159" s="39"/>
     </row>
-    <row r="160" spans="66:67">
+    <row r="160" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN160" s="38"/>
       <c r="BO160" s="39"/>
     </row>
-    <row r="161" spans="66:67">
+    <row r="161" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN161" s="38"/>
       <c r="BO161" s="39"/>
     </row>
-    <row r="162" spans="66:67">
+    <row r="162" spans="66:67" x14ac:dyDescent="0.35">
       <c r="BN162" s="38"/>
       <c r="BO162" s="39"/>
     </row>
@@ -10862,13 +10894,13 @@
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:BO50"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="31.5703125" customWidth="1"/>
-    <col min="67" max="67" width="11.5703125" style="41"/>
+    <col min="1" max="1" width="31.54296875" customWidth="1"/>
+    <col min="67" max="67" width="11.54296875" style="41"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:67" s="2" customFormat="1">
+    <row r="1" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="9" t="s">
         <v>34</v>
       </c>
@@ -11069,7 +11101,7 @@
       </c>
       <c r="BO1" s="39"/>
     </row>
-    <row r="2" spans="1:67" s="2" customFormat="1">
+    <row r="2" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
         <v>35</v>
       </c>
@@ -11270,7 +11302,7 @@
       </c>
       <c r="BO2" s="39"/>
     </row>
-    <row r="3" spans="1:67" s="2" customFormat="1">
+    <row r="3" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>36</v>
       </c>
@@ -11471,7 +11503,7 @@
       </c>
       <c r="BO3" s="39"/>
     </row>
-    <row r="4" spans="1:67" s="2" customFormat="1">
+    <row r="4" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="11" t="s">
         <v>48</v>
       </c>
@@ -11517,7 +11549,9 @@
       <c r="O4" s="4">
         <v>0</v>
       </c>
-      <c r="P4" s="4"/>
+      <c r="P4" s="4">
+        <v>0</v>
+      </c>
       <c r="Q4" s="4"/>
       <c r="R4" s="4"/>
       <c r="S4" s="4"/>
@@ -11570,7 +11604,7 @@
       <c r="BN4" s="4"/>
       <c r="BO4" s="39"/>
     </row>
-    <row r="5" spans="1:67" s="2" customFormat="1">
+    <row r="5" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
         <v>49</v>
       </c>
@@ -11616,7 +11650,9 @@
       <c r="O5" s="4">
         <v>0</v>
       </c>
-      <c r="P5" s="4"/>
+      <c r="P5" s="4">
+        <v>0</v>
+      </c>
       <c r="Q5" s="4"/>
       <c r="R5" s="4"/>
       <c r="S5" s="4"/>
@@ -11669,7 +11705,7 @@
       <c r="BN5" s="4"/>
       <c r="BO5" s="39"/>
     </row>
-    <row r="6" spans="1:67" s="2" customFormat="1">
+    <row r="6" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
         <v>50</v>
       </c>
@@ -11715,7 +11751,9 @@
       <c r="O6" s="4">
         <v>0</v>
       </c>
-      <c r="P6" s="4"/>
+      <c r="P6" s="4">
+        <v>0</v>
+      </c>
       <c r="Q6" s="4"/>
       <c r="R6" s="4"/>
       <c r="S6" s="4"/>
@@ -11768,7 +11806,7 @@
       <c r="BN6" s="4"/>
       <c r="BO6" s="39"/>
     </row>
-    <row r="7" spans="1:67" s="2" customFormat="1">
+    <row r="7" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
         <v>51</v>
       </c>
@@ -11814,7 +11852,9 @@
       <c r="O7" s="4">
         <v>0</v>
       </c>
-      <c r="P7" s="4"/>
+      <c r="P7" s="4">
+        <v>0</v>
+      </c>
       <c r="Q7" s="4"/>
       <c r="R7" s="4"/>
       <c r="S7" s="4"/>
@@ -11867,7 +11907,7 @@
       <c r="BN7" s="4"/>
       <c r="BO7" s="39"/>
     </row>
-    <row r="8" spans="1:67" s="2" customFormat="1">
+    <row r="8" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="8" t="s">
         <v>52</v>
       </c>
@@ -11913,7 +11953,9 @@
       <c r="O8" s="4">
         <v>0</v>
       </c>
-      <c r="P8" s="4"/>
+      <c r="P8" s="4">
+        <v>0</v>
+      </c>
       <c r="Q8" s="4"/>
       <c r="R8" s="4"/>
       <c r="S8" s="4"/>
@@ -11966,7 +12008,7 @@
       <c r="BN8" s="4"/>
       <c r="BO8" s="39"/>
     </row>
-    <row r="9" spans="1:67" s="2" customFormat="1">
+    <row r="9" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A9" s="12"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -12035,7 +12077,7 @@
       <c r="BN9" s="6"/>
       <c r="BO9" s="39"/>
     </row>
-    <row r="10" spans="1:67" hidden="1">
+    <row r="10" spans="1:67" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
         <v>53</v>
       </c>
@@ -12131,7 +12173,7 @@
       <c r="BM10" s="4"/>
       <c r="BN10" s="4"/>
     </row>
-    <row r="11" spans="1:67">
+    <row r="11" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
         <v>54</v>
       </c>
@@ -12177,7 +12219,9 @@
       <c r="O11" s="4">
         <v>0</v>
       </c>
-      <c r="P11" s="4"/>
+      <c r="P11" s="4">
+        <v>0</v>
+      </c>
       <c r="Q11" s="4"/>
       <c r="R11" s="4"/>
       <c r="S11" s="4"/>
@@ -12229,7 +12273,7 @@
       <c r="BM11" s="4"/>
       <c r="BN11" s="4"/>
     </row>
-    <row r="12" spans="1:67">
+    <row r="12" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A12" s="8" t="s">
         <v>55</v>
       </c>
@@ -12275,7 +12319,9 @@
       <c r="O12" s="4">
         <v>0</v>
       </c>
-      <c r="P12" s="4"/>
+      <c r="P12" s="4">
+        <v>0</v>
+      </c>
       <c r="Q12" s="4"/>
       <c r="R12" s="4"/>
       <c r="S12" s="4"/>
@@ -12327,7 +12373,7 @@
       <c r="BM12" s="4"/>
       <c r="BN12" s="4"/>
     </row>
-    <row r="13" spans="1:67">
+    <row r="13" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A13" s="8" t="s">
         <v>56</v>
       </c>
@@ -12373,7 +12419,9 @@
       <c r="O13" s="4">
         <v>0</v>
       </c>
-      <c r="P13" s="4"/>
+      <c r="P13" s="4">
+        <v>0</v>
+      </c>
       <c r="Q13" s="4"/>
       <c r="R13" s="4"/>
       <c r="S13" s="4"/>
@@ -12425,7 +12473,7 @@
       <c r="BM13" s="4"/>
       <c r="BN13" s="4"/>
     </row>
-    <row r="14" spans="1:67">
+    <row r="14" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
         <v>57</v>
       </c>
@@ -12471,7 +12519,9 @@
       <c r="O14" s="4">
         <v>0</v>
       </c>
-      <c r="P14" s="4"/>
+      <c r="P14" s="4">
+        <v>0</v>
+      </c>
       <c r="Q14" s="4"/>
       <c r="R14" s="4"/>
       <c r="S14" s="4"/>
@@ -12523,7 +12573,7 @@
       <c r="BM14" s="4"/>
       <c r="BN14" s="4"/>
     </row>
-    <row r="15" spans="1:67">
+    <row r="15" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A15" s="8" t="s">
         <v>58</v>
       </c>
@@ -12569,7 +12619,9 @@
       <c r="O15" s="4">
         <v>0</v>
       </c>
-      <c r="P15" s="4"/>
+      <c r="P15" s="4">
+        <v>0</v>
+      </c>
       <c r="Q15" s="4"/>
       <c r="R15" s="4"/>
       <c r="S15" s="4"/>
@@ -12621,7 +12673,7 @@
       <c r="BM15" s="4"/>
       <c r="BN15" s="4"/>
     </row>
-    <row r="16" spans="1:67">
+    <row r="16" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A16" s="8" t="s">
         <v>59</v>
       </c>
@@ -12667,7 +12719,9 @@
       <c r="O16" s="4">
         <v>0</v>
       </c>
-      <c r="P16" s="4"/>
+      <c r="P16" s="4">
+        <v>0</v>
+      </c>
       <c r="Q16" s="4"/>
       <c r="R16" s="4"/>
       <c r="S16" s="4"/>
@@ -12719,7 +12773,7 @@
       <c r="BM16" s="4"/>
       <c r="BN16" s="4"/>
     </row>
-    <row r="17" spans="1:67">
+    <row r="17" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A17" s="12"/>
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
@@ -12787,7 +12841,7 @@
       <c r="BM17" s="14"/>
       <c r="BN17" s="14"/>
     </row>
-    <row r="18" spans="1:67" s="2" customFormat="1">
+    <row r="18" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A18" s="8" t="s">
         <v>31</v>
       </c>
@@ -12833,7 +12887,9 @@
       <c r="O18" s="4">
         <v>0</v>
       </c>
-      <c r="P18" s="4"/>
+      <c r="P18" s="4">
+        <v>0</v>
+      </c>
       <c r="Q18" s="4"/>
       <c r="R18" s="4"/>
       <c r="S18" s="4"/>
@@ -12886,7 +12942,7 @@
       <c r="BN18" s="4"/>
       <c r="BO18" s="39"/>
     </row>
-    <row r="19" spans="1:67" s="2" customFormat="1">
+    <row r="19" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A19" s="8" t="s">
         <v>60</v>
       </c>
@@ -12932,7 +12988,9 @@
       <c r="O19" s="4">
         <v>0</v>
       </c>
-      <c r="P19" s="4"/>
+      <c r="P19" s="4">
+        <v>0</v>
+      </c>
       <c r="Q19" s="4"/>
       <c r="R19" s="4"/>
       <c r="S19" s="4"/>
@@ -12985,7 +13043,7 @@
       <c r="BN19" s="4"/>
       <c r="BO19" s="39"/>
     </row>
-    <row r="20" spans="1:67" s="2" customFormat="1">
+    <row r="20" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A20" s="8" t="s">
         <v>61</v>
       </c>
@@ -13031,7 +13089,9 @@
       <c r="O20" s="4">
         <v>0</v>
       </c>
-      <c r="P20" s="4"/>
+      <c r="P20" s="4">
+        <v>0</v>
+      </c>
       <c r="Q20" s="4"/>
       <c r="R20" s="4"/>
       <c r="S20" s="4"/>
@@ -13084,7 +13144,7 @@
       <c r="BN20" s="4"/>
       <c r="BO20" s="39"/>
     </row>
-    <row r="21" spans="1:67" s="2" customFormat="1">
+    <row r="21" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A21" s="8" t="s">
         <v>62</v>
       </c>
@@ -13130,7 +13190,9 @@
       <c r="O21" s="4">
         <v>0</v>
       </c>
-      <c r="P21" s="4"/>
+      <c r="P21" s="4">
+        <v>0</v>
+      </c>
       <c r="Q21" s="4"/>
       <c r="R21" s="4"/>
       <c r="S21" s="4"/>
@@ -13183,7 +13245,7 @@
       <c r="BN21" s="4"/>
       <c r="BO21" s="39"/>
     </row>
-    <row r="22" spans="1:67" s="2" customFormat="1">
+    <row r="22" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
         <v>63</v>
       </c>
@@ -13229,7 +13291,9 @@
       <c r="O22" s="4">
         <v>0</v>
       </c>
-      <c r="P22" s="4"/>
+      <c r="P22" s="4">
+        <v>0</v>
+      </c>
       <c r="Q22" s="4"/>
       <c r="R22" s="4"/>
       <c r="S22" s="4"/>
@@ -13282,7 +13346,7 @@
       <c r="BN22" s="4"/>
       <c r="BO22" s="39"/>
     </row>
-    <row r="23" spans="1:67" s="2" customFormat="1">
+    <row r="23" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A23" s="6"/>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
@@ -13351,25 +13415,25 @@
       <c r="BN23" s="6"/>
       <c r="BO23" s="39"/>
     </row>
-    <row r="24" spans="1:67" s="2" customFormat="1">
+    <row r="24" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="BO24" s="39"/>
     </row>
-    <row r="25" spans="1:67" s="2" customFormat="1">
+    <row r="25" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="BO25" s="39"/>
     </row>
-    <row r="26" spans="1:67" s="2" customFormat="1" hidden="1">
+    <row r="26" spans="1:67" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="BO26" s="39"/>
     </row>
-    <row r="27" spans="1:67" s="2" customFormat="1" hidden="1">
+    <row r="27" spans="1:67" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="BO27" s="39"/>
     </row>
-    <row r="28" spans="1:67" s="2" customFormat="1" hidden="1">
+    <row r="28" spans="1:67" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="BO28" s="39"/>
     </row>
-    <row r="29" spans="1:67" s="2" customFormat="1" hidden="1">
+    <row r="29" spans="1:67" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="BO29" s="39"/>
     </row>
-    <row r="30" spans="1:67" s="2" customFormat="1">
+    <row r="30" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A30" s="7" t="s">
         <v>46</v>
       </c>
@@ -13440,7 +13504,7 @@
       <c r="BN30" s="6"/>
       <c r="BO30" s="39"/>
     </row>
-    <row r="31" spans="1:67" s="2" customFormat="1">
+    <row r="31" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A31" s="7"/>
       <c r="B31" s="17" t="s">
         <v>64</v>
@@ -13639,7 +13703,7 @@
       </c>
       <c r="BO31" s="39"/>
     </row>
-    <row r="32" spans="1:67" s="2" customFormat="1">
+    <row r="32" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A32" s="11" t="s">
         <v>48</v>
       </c>
@@ -13905,7 +13969,7 @@
       </c>
       <c r="BO32" s="39"/>
     </row>
-    <row r="33" spans="1:67" s="2" customFormat="1">
+    <row r="33" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A33" s="8" t="s">
         <v>49</v>
       </c>
@@ -14171,7 +14235,7 @@
       </c>
       <c r="BO33" s="39"/>
     </row>
-    <row r="34" spans="1:67" s="2" customFormat="1">
+    <row r="34" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A34" s="8" t="s">
         <v>50</v>
       </c>
@@ -14437,7 +14501,7 @@
       </c>
       <c r="BO34" s="39"/>
     </row>
-    <row r="35" spans="1:67" s="2" customFormat="1">
+    <row r="35" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A35" s="8" t="s">
         <v>51</v>
       </c>
@@ -14703,7 +14767,7 @@
       </c>
       <c r="BO35" s="39"/>
     </row>
-    <row r="36" spans="1:67" s="2" customFormat="1">
+    <row r="36" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A36" s="8" t="s">
         <v>52</v>
       </c>
@@ -14969,7 +15033,7 @@
       </c>
       <c r="BO36" s="39"/>
     </row>
-    <row r="37" spans="1:67" s="2" customFormat="1">
+    <row r="37" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A37" s="12"/>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -15038,7 +15102,7 @@
       <c r="BN37" s="6"/>
       <c r="BO37" s="39"/>
     </row>
-    <row r="38" spans="1:67" hidden="1">
+    <row r="38" spans="1:67" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="7" t="s">
         <v>53</v>
       </c>
@@ -15120,7 +15184,7 @@
       <c r="BM38" s="5"/>
       <c r="BN38" s="5"/>
     </row>
-    <row r="39" spans="1:67">
+    <row r="39" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A39" s="8" t="s">
         <v>54</v>
       </c>
@@ -15385,7 +15449,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:67">
+    <row r="40" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A40" s="8" t="s">
         <v>55</v>
       </c>
@@ -15650,7 +15714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:67">
+    <row r="41" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A41" s="8" t="s">
         <v>56</v>
       </c>
@@ -15915,7 +15979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:67">
+    <row r="42" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A42" s="8" t="s">
         <v>57</v>
       </c>
@@ -16180,7 +16244,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:67">
+    <row r="43" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A43" s="8" t="s">
         <v>58</v>
       </c>
@@ -16445,7 +16509,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:67">
+    <row r="44" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A44" s="8" t="s">
         <v>59</v>
       </c>
@@ -16710,7 +16774,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:67">
+    <row r="45" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A45" s="12"/>
       <c r="B45" s="14"/>
       <c r="C45" s="14"/>
@@ -16778,7 +16842,7 @@
       <c r="BM45" s="14"/>
       <c r="BN45" s="14"/>
     </row>
-    <row r="46" spans="1:67" s="2" customFormat="1">
+    <row r="46" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A46" s="8" t="s">
         <v>31</v>
       </c>
@@ -17044,7 +17108,7 @@
       </c>
       <c r="BO46" s="39"/>
     </row>
-    <row r="47" spans="1:67" s="2" customFormat="1">
+    <row r="47" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A47" s="8" t="s">
         <v>60</v>
       </c>
@@ -17310,7 +17374,7 @@
       </c>
       <c r="BO47" s="39"/>
     </row>
-    <row r="48" spans="1:67" s="2" customFormat="1">
+    <row r="48" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A48" s="8" t="s">
         <v>61</v>
       </c>
@@ -17576,7 +17640,7 @@
       </c>
       <c r="BO48" s="39"/>
     </row>
-    <row r="49" spans="1:67" s="2" customFormat="1">
+    <row r="49" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A49" s="8" t="s">
         <v>62</v>
       </c>
@@ -17842,7 +17906,7 @@
       </c>
       <c r="BO49" s="39"/>
     </row>
-    <row r="50" spans="1:67" s="2" customFormat="1">
+    <row r="50" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A50" s="8" t="s">
         <v>63</v>
       </c>
@@ -18142,43 +18206,43 @@
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:BO56"/>
-  <sheetFormatPr defaultColWidth="10.42578125" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="10.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20" style="2" customWidth="1"/>
-    <col min="2" max="5" width="10.42578125" style="2"/>
-    <col min="6" max="6" width="10.42578125" style="53"/>
-    <col min="7" max="10" width="10.42578125" style="2"/>
-    <col min="11" max="11" width="10.42578125" style="53"/>
-    <col min="12" max="14" width="10.42578125" style="2"/>
-    <col min="15" max="15" width="10.42578125" style="53"/>
-    <col min="16" max="18" width="10.42578125" style="2"/>
-    <col min="19" max="19" width="10.42578125" style="53"/>
-    <col min="20" max="22" width="10.42578125" style="2"/>
-    <col min="23" max="23" width="10.42578125" style="53"/>
-    <col min="24" max="27" width="10.42578125" style="2"/>
-    <col min="28" max="28" width="10.42578125" style="53"/>
-    <col min="29" max="31" width="10.42578125" style="2"/>
-    <col min="32" max="32" width="10.42578125" style="53"/>
-    <col min="33" max="36" width="10.42578125" style="2"/>
-    <col min="37" max="37" width="10.42578125" style="53"/>
-    <col min="38" max="40" width="10.42578125" style="2"/>
-    <col min="41" max="41" width="10.42578125" style="53"/>
-    <col min="42" max="44" width="10.42578125" style="2"/>
-    <col min="45" max="45" width="10.42578125" style="53"/>
-    <col min="46" max="49" width="10.42578125" style="2"/>
-    <col min="50" max="50" width="10.42578125" style="53"/>
-    <col min="51" max="53" width="10.42578125" style="2"/>
-    <col min="54" max="54" width="10.42578125" style="53"/>
-    <col min="55" max="57" width="10.42578125" style="2"/>
-    <col min="58" max="58" width="10.42578125" style="53"/>
-    <col min="59" max="62" width="10.42578125" style="2"/>
-    <col min="63" max="63" width="10.42578125" style="53"/>
-    <col min="64" max="66" width="10.42578125" style="2"/>
-    <col min="67" max="67" width="10.42578125" style="39"/>
-    <col min="68" max="16384" width="10.42578125" style="2"/>
+    <col min="2" max="5" width="10.453125" style="2"/>
+    <col min="6" max="6" width="10.453125" style="53"/>
+    <col min="7" max="10" width="10.453125" style="2"/>
+    <col min="11" max="11" width="10.453125" style="53"/>
+    <col min="12" max="14" width="10.453125" style="2"/>
+    <col min="15" max="15" width="10.453125" style="53"/>
+    <col min="16" max="18" width="10.453125" style="2"/>
+    <col min="19" max="19" width="10.453125" style="53"/>
+    <col min="20" max="22" width="10.453125" style="2"/>
+    <col min="23" max="23" width="10.453125" style="53"/>
+    <col min="24" max="27" width="10.453125" style="2"/>
+    <col min="28" max="28" width="10.453125" style="53"/>
+    <col min="29" max="31" width="10.453125" style="2"/>
+    <col min="32" max="32" width="10.453125" style="53"/>
+    <col min="33" max="36" width="10.453125" style="2"/>
+    <col min="37" max="37" width="10.453125" style="53"/>
+    <col min="38" max="40" width="10.453125" style="2"/>
+    <col min="41" max="41" width="10.453125" style="53"/>
+    <col min="42" max="44" width="10.453125" style="2"/>
+    <col min="45" max="45" width="10.453125" style="53"/>
+    <col min="46" max="49" width="10.453125" style="2"/>
+    <col min="50" max="50" width="10.453125" style="53"/>
+    <col min="51" max="53" width="10.453125" style="2"/>
+    <col min="54" max="54" width="10.453125" style="53"/>
+    <col min="55" max="57" width="10.453125" style="2"/>
+    <col min="58" max="58" width="10.453125" style="53"/>
+    <col min="59" max="62" width="10.453125" style="2"/>
+    <col min="63" max="63" width="10.453125" style="53"/>
+    <col min="64" max="66" width="10.453125" style="2"/>
+    <col min="67" max="67" width="10.453125" style="39"/>
+    <col min="68" max="16384" width="10.453125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:66">
+    <row r="1" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A1" s="9" t="s">
         <v>34</v>
       </c>
@@ -18428,7 +18492,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="2" spans="1:66">
+    <row r="2" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
         <v>35</v>
       </c>
@@ -18628,7 +18692,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:66">
+    <row r="3" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>36</v>
       </c>
@@ -18828,7 +18892,7 @@
         <v>46444</v>
       </c>
     </row>
-    <row r="4" spans="1:66">
+    <row r="4" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>37</v>
       </c>
@@ -18898,7 +18962,7 @@
       <c r="BM4" s="6"/>
       <c r="BN4" s="6"/>
     </row>
-    <row r="5" spans="1:66">
+    <row r="5" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
         <v>38</v>
       </c>
@@ -18996,7 +19060,7 @@
       <c r="BM5" s="4"/>
       <c r="BN5" s="4"/>
     </row>
-    <row r="6" spans="1:66">
+    <row r="6" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
         <v>39</v>
       </c>
@@ -19094,7 +19158,7 @@
       <c r="BM6" s="4"/>
       <c r="BN6" s="4"/>
     </row>
-    <row r="7" spans="1:66">
+    <row r="7" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
         <v>40</v>
       </c>
@@ -19192,7 +19256,7 @@
       <c r="BM7" s="4"/>
       <c r="BN7" s="4"/>
     </row>
-    <row r="8" spans="1:66">
+    <row r="8" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
         <v>41</v>
       </c>
@@ -19262,7 +19326,7 @@
       <c r="BM8" s="6"/>
       <c r="BN8" s="6"/>
     </row>
-    <row r="9" spans="1:66">
+    <row r="9" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A9" s="8" t="s">
         <v>38</v>
       </c>
@@ -19360,7 +19424,7 @@
       <c r="BM9" s="4"/>
       <c r="BN9" s="4"/>
     </row>
-    <row r="10" spans="1:66">
+    <row r="10" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
         <v>39</v>
       </c>
@@ -19458,7 +19522,7 @@
       <c r="BM10" s="4"/>
       <c r="BN10" s="4"/>
     </row>
-    <row r="11" spans="1:66">
+    <row r="11" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
         <v>40</v>
       </c>
@@ -19556,7 +19620,7 @@
       <c r="BM11" s="4"/>
       <c r="BN11" s="4"/>
     </row>
-    <row r="12" spans="1:66">
+    <row r="12" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
         <v>42</v>
       </c>
@@ -19626,7 +19690,7 @@
       <c r="BM12" s="7"/>
       <c r="BN12" s="7"/>
     </row>
-    <row r="13" spans="1:66">
+    <row r="13" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A13" s="8" t="s">
         <v>38</v>
       </c>
@@ -19724,7 +19788,7 @@
       <c r="BM13" s="4"/>
       <c r="BN13" s="4"/>
     </row>
-    <row r="14" spans="1:66">
+    <row r="14" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
         <v>39</v>
       </c>
@@ -19822,7 +19886,7 @@
       <c r="BM14" s="4"/>
       <c r="BN14" s="4"/>
     </row>
-    <row r="15" spans="1:66">
+    <row r="15" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A15" s="8" t="s">
         <v>40</v>
       </c>
@@ -19920,7 +19984,7 @@
       <c r="BM15" s="4"/>
       <c r="BN15" s="4"/>
     </row>
-    <row r="16" spans="1:66">
+    <row r="16" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
         <v>43</v>
       </c>
@@ -19990,7 +20054,7 @@
       <c r="BM16" s="7"/>
       <c r="BN16" s="7"/>
     </row>
-    <row r="17" spans="1:66">
+    <row r="17" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A17" s="8" t="s">
         <v>38</v>
       </c>
@@ -20088,7 +20152,7 @@
       <c r="BM17" s="4"/>
       <c r="BN17" s="4"/>
     </row>
-    <row r="18" spans="1:66">
+    <row r="18" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A18" s="8" t="s">
         <v>39</v>
       </c>
@@ -20186,7 +20250,7 @@
       <c r="BM18" s="4"/>
       <c r="BN18" s="4"/>
     </row>
-    <row r="19" spans="1:66">
+    <row r="19" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A19" s="8" t="s">
         <v>40</v>
       </c>
@@ -20284,7 +20348,7 @@
       <c r="BM19" s="4"/>
       <c r="BN19" s="4"/>
     </row>
-    <row r="20" spans="1:66">
+    <row r="20" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A20" s="7" t="s">
         <v>44</v>
       </c>
@@ -20354,7 +20418,7 @@
       <c r="BM20" s="7"/>
       <c r="BN20" s="7"/>
     </row>
-    <row r="21" spans="1:66">
+    <row r="21" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A21" s="8" t="s">
         <v>38</v>
       </c>
@@ -20452,7 +20516,7 @@
       <c r="BM21" s="4"/>
       <c r="BN21" s="4"/>
     </row>
-    <row r="22" spans="1:66">
+    <row r="22" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
         <v>45</v>
       </c>
@@ -20522,7 +20586,7 @@
       <c r="BM22" s="7"/>
       <c r="BN22" s="7"/>
     </row>
-    <row r="23" spans="1:66">
+    <row r="23" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A23" s="8" t="s">
         <v>38</v>
       </c>
@@ -20620,7 +20684,7 @@
       <c r="BM23" s="4"/>
       <c r="BN23" s="4"/>
     </row>
-    <row r="24" spans="1:66">
+    <row r="24" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A24" s="8" t="s">
         <v>39</v>
       </c>
@@ -20718,7 +20782,7 @@
       <c r="BM24" s="4"/>
       <c r="BN24" s="4"/>
     </row>
-    <row r="25" spans="1:66">
+    <row r="25" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A25" s="8" t="s">
         <v>40</v>
       </c>
@@ -20816,7 +20880,7 @@
       <c r="BM25" s="4"/>
       <c r="BN25" s="4"/>
     </row>
-    <row r="26" spans="1:66">
+    <row r="26" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A26" s="6"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -20884,7 +20948,7 @@
       <c r="BM26" s="6"/>
       <c r="BN26" s="6"/>
     </row>
-    <row r="29" spans="1:66">
+    <row r="29" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A29" s="7" t="s">
         <v>46</v>
       </c>
@@ -20954,7 +21018,7 @@
       <c r="BM29" s="6"/>
       <c r="BN29" s="6"/>
     </row>
-    <row r="30" spans="1:66" hidden="1">
+    <row r="30" spans="1:66" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="7" t="s">
         <v>47</v>
       </c>
@@ -21032,7 +21096,7 @@
       <c r="BM30" s="10"/>
       <c r="BN30" s="10"/>
     </row>
-    <row r="31" spans="1:66" hidden="1">
+    <row r="31" spans="1:66" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="8" t="s">
         <v>38</v>
       </c>
@@ -21102,7 +21166,7 @@
       <c r="BM31" s="5"/>
       <c r="BN31" s="5"/>
     </row>
-    <row r="32" spans="1:66" hidden="1">
+    <row r="32" spans="1:66" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="8" t="s">
         <v>39</v>
       </c>
@@ -21172,7 +21236,7 @@
       <c r="BM32" s="5"/>
       <c r="BN32" s="5"/>
     </row>
-    <row r="33" spans="1:66" hidden="1">
+    <row r="33" spans="1:66" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="8" t="s">
         <v>40</v>
       </c>
@@ -21242,7 +21306,7 @@
       <c r="BM33" s="5"/>
       <c r="BN33" s="5"/>
     </row>
-    <row r="34" spans="1:66">
+    <row r="34" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A34" s="7" t="s">
         <v>37</v>
       </c>
@@ -21312,7 +21376,7 @@
       <c r="BM34" s="6"/>
       <c r="BN34" s="6"/>
     </row>
-    <row r="35" spans="1:66">
+    <row r="35" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A35" s="8" t="s">
         <v>38</v>
       </c>
@@ -21577,7 +21641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:66">
+    <row r="36" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A36" s="8" t="s">
         <v>39</v>
       </c>
@@ -21842,7 +21906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:66">
+    <row r="37" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A37" s="8" t="s">
         <v>40</v>
       </c>
@@ -22107,7 +22171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:66">
+    <row r="38" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A38" s="7" t="s">
         <v>41</v>
       </c>
@@ -22177,7 +22241,7 @@
       <c r="BM38" s="6"/>
       <c r="BN38" s="6"/>
     </row>
-    <row r="39" spans="1:66">
+    <row r="39" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A39" s="8" t="s">
         <v>38</v>
       </c>
@@ -22442,7 +22506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:66">
+    <row r="40" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A40" s="8" t="s">
         <v>39</v>
       </c>
@@ -22707,7 +22771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:66">
+    <row r="41" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A41" s="8" t="s">
         <v>40</v>
       </c>
@@ -22972,7 +23036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:66">
+    <row r="42" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A42" s="7" t="s">
         <v>42</v>
       </c>
@@ -23042,7 +23106,7 @@
       <c r="BM42" s="6"/>
       <c r="BN42" s="6"/>
     </row>
-    <row r="43" spans="1:66">
+    <row r="43" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A43" s="8" t="s">
         <v>38</v>
       </c>
@@ -23307,7 +23371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:66">
+    <row r="44" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A44" s="8" t="s">
         <v>39</v>
       </c>
@@ -23572,7 +23636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:66">
+    <row r="45" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A45" s="8" t="s">
         <v>40</v>
       </c>
@@ -23837,7 +23901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:66">
+    <row r="46" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A46" s="7" t="s">
         <v>43</v>
       </c>
@@ -23907,7 +23971,7 @@
       <c r="BM46" s="6"/>
       <c r="BN46" s="6"/>
     </row>
-    <row r="47" spans="1:66">
+    <row r="47" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A47" s="8" t="s">
         <v>38</v>
       </c>
@@ -24172,7 +24236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:66">
+    <row r="48" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A48" s="8" t="s">
         <v>39</v>
       </c>
@@ -24437,7 +24501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:66">
+    <row r="49" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A49" s="8" t="s">
         <v>40</v>
       </c>
@@ -24702,7 +24766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:66">
+    <row r="50" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A50" s="7" t="s">
         <v>44</v>
       </c>
@@ -24772,7 +24836,7 @@
       <c r="BM50" s="6"/>
       <c r="BN50" s="6"/>
     </row>
-    <row r="51" spans="1:66">
+    <row r="51" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A51" s="8" t="s">
         <v>38</v>
       </c>
@@ -25037,7 +25101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:66">
+    <row r="52" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A52" s="7" t="s">
         <v>45</v>
       </c>
@@ -25107,7 +25171,7 @@
       <c r="BM52" s="6"/>
       <c r="BN52" s="6"/>
     </row>
-    <row r="53" spans="1:66">
+    <row r="53" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A53" s="8" t="s">
         <v>38</v>
       </c>
@@ -25372,7 +25436,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:66">
+    <row r="54" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A54" s="8" t="s">
         <v>39</v>
       </c>
@@ -25637,7 +25701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:66">
+    <row r="55" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A55" s="8" t="s">
         <v>40</v>
       </c>
@@ -25902,7 +25966,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:66">
+    <row r="56" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A56" s="6"/>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
@@ -26004,9 +26068,9 @@
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:BO50"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="32.140625" customWidth="1"/>
+    <col min="1" max="1" width="32.1796875" customWidth="1"/>
     <col min="6" max="6" width="11" style="57"/>
     <col min="11" max="11" width="11" style="57"/>
     <col min="15" max="15" width="11" style="57"/>
@@ -26021,10 +26085,10 @@
     <col min="54" max="54" width="11" style="57"/>
     <col min="58" max="58" width="11" style="57"/>
     <col min="63" max="63" width="11" style="57"/>
-    <col min="67" max="67" width="10.85546875" style="41" customWidth="1"/>
+    <col min="67" max="67" width="10.81640625" style="41" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:67" s="2" customFormat="1">
+    <row r="1" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="9" t="s">
         <v>34</v>
       </c>
@@ -26275,7 +26339,7 @@
       </c>
       <c r="BO1" s="39"/>
     </row>
-    <row r="2" spans="1:67" s="2" customFormat="1">
+    <row r="2" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
         <v>35</v>
       </c>
@@ -26476,7 +26540,7 @@
       </c>
       <c r="BO2" s="39"/>
     </row>
-    <row r="3" spans="1:67" s="2" customFormat="1">
+    <row r="3" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>36</v>
       </c>
@@ -26677,7 +26741,7 @@
       </c>
       <c r="BO3" s="39"/>
     </row>
-    <row r="4" spans="1:67" s="2" customFormat="1">
+    <row r="4" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="11" t="s">
         <v>48</v>
       </c>
@@ -26776,7 +26840,7 @@
       <c r="BN4" s="4"/>
       <c r="BO4" s="39"/>
     </row>
-    <row r="5" spans="1:67" s="2" customFormat="1">
+    <row r="5" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
         <v>49</v>
       </c>
@@ -26875,7 +26939,7 @@
       <c r="BN5" s="4"/>
       <c r="BO5" s="39"/>
     </row>
-    <row r="6" spans="1:67" s="2" customFormat="1">
+    <row r="6" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
         <v>50</v>
       </c>
@@ -26974,7 +27038,7 @@
       <c r="BN6" s="4"/>
       <c r="BO6" s="39"/>
     </row>
-    <row r="7" spans="1:67" s="2" customFormat="1">
+    <row r="7" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
         <v>51</v>
       </c>
@@ -27073,7 +27137,7 @@
       <c r="BN7" s="4"/>
       <c r="BO7" s="39"/>
     </row>
-    <row r="8" spans="1:67" s="2" customFormat="1">
+    <row r="8" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="8" t="s">
         <v>52</v>
       </c>
@@ -27172,7 +27236,7 @@
       <c r="BN8" s="4"/>
       <c r="BO8" s="39"/>
     </row>
-    <row r="9" spans="1:67" s="2" customFormat="1">
+    <row r="9" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A9" s="12"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -27241,7 +27305,7 @@
       <c r="BN9" s="6"/>
       <c r="BO9" s="39"/>
     </row>
-    <row r="10" spans="1:67" hidden="1">
+    <row r="10" spans="1:67" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
         <v>53</v>
       </c>
@@ -27337,7 +27401,7 @@
       <c r="BM10" s="4"/>
       <c r="BN10" s="4"/>
     </row>
-    <row r="11" spans="1:67">
+    <row r="11" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
         <v>54</v>
       </c>
@@ -27435,7 +27499,7 @@
       <c r="BM11" s="4"/>
       <c r="BN11" s="4"/>
     </row>
-    <row r="12" spans="1:67">
+    <row r="12" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A12" s="8" t="s">
         <v>55</v>
       </c>
@@ -27533,7 +27597,7 @@
       <c r="BM12" s="4"/>
       <c r="BN12" s="4"/>
     </row>
-    <row r="13" spans="1:67">
+    <row r="13" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A13" s="8" t="s">
         <v>56</v>
       </c>
@@ -27631,7 +27695,7 @@
       <c r="BM13" s="4"/>
       <c r="BN13" s="4"/>
     </row>
-    <row r="14" spans="1:67">
+    <row r="14" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
         <v>57</v>
       </c>
@@ -27729,7 +27793,7 @@
       <c r="BM14" s="4"/>
       <c r="BN14" s="4"/>
     </row>
-    <row r="15" spans="1:67">
+    <row r="15" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A15" s="8" t="s">
         <v>58</v>
       </c>
@@ -27827,7 +27891,7 @@
       <c r="BM15" s="4"/>
       <c r="BN15" s="4"/>
     </row>
-    <row r="16" spans="1:67">
+    <row r="16" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A16" s="8" t="s">
         <v>59</v>
       </c>
@@ -27925,7 +27989,7 @@
       <c r="BM16" s="4"/>
       <c r="BN16" s="4"/>
     </row>
-    <row r="17" spans="1:67">
+    <row r="17" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A17" s="12"/>
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
@@ -27993,7 +28057,7 @@
       <c r="BM17" s="14"/>
       <c r="BN17" s="14"/>
     </row>
-    <row r="18" spans="1:67" s="2" customFormat="1">
+    <row r="18" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A18" s="8" t="s">
         <v>31</v>
       </c>
@@ -28092,7 +28156,7 @@
       <c r="BN18" s="4"/>
       <c r="BO18" s="39"/>
     </row>
-    <row r="19" spans="1:67" s="2" customFormat="1">
+    <row r="19" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A19" s="8" t="s">
         <v>60</v>
       </c>
@@ -28191,7 +28255,7 @@
       <c r="BN19" s="4"/>
       <c r="BO19" s="39"/>
     </row>
-    <row r="20" spans="1:67" s="2" customFormat="1">
+    <row r="20" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A20" s="8" t="s">
         <v>61</v>
       </c>
@@ -28290,7 +28354,7 @@
       <c r="BN20" s="4"/>
       <c r="BO20" s="39"/>
     </row>
-    <row r="21" spans="1:67" s="2" customFormat="1">
+    <row r="21" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A21" s="8" t="s">
         <v>62</v>
       </c>
@@ -28389,7 +28453,7 @@
       <c r="BN21" s="4"/>
       <c r="BO21" s="39"/>
     </row>
-    <row r="22" spans="1:67" s="2" customFormat="1">
+    <row r="22" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
         <v>63</v>
       </c>
@@ -28488,7 +28552,7 @@
       <c r="BN22" s="4"/>
       <c r="BO22" s="39"/>
     </row>
-    <row r="23" spans="1:67" s="2" customFormat="1">
+    <row r="23" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A23" s="6"/>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
@@ -28557,7 +28621,7 @@
       <c r="BN23" s="6"/>
       <c r="BO23" s="39"/>
     </row>
-    <row r="24" spans="1:67" s="2" customFormat="1" hidden="1">
+    <row r="24" spans="1:67" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="F24" s="53"/>
       <c r="K24" s="53"/>
       <c r="O24" s="53"/>
@@ -28574,7 +28638,7 @@
       <c r="BK24" s="53"/>
       <c r="BO24" s="39"/>
     </row>
-    <row r="25" spans="1:67" s="2" customFormat="1" hidden="1">
+    <row r="25" spans="1:67" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="F25" s="53"/>
       <c r="K25" s="53"/>
       <c r="O25" s="53"/>
@@ -28591,7 +28655,7 @@
       <c r="BK25" s="53"/>
       <c r="BO25" s="39"/>
     </row>
-    <row r="26" spans="1:67" s="2" customFormat="1" hidden="1">
+    <row r="26" spans="1:67" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="F26" s="53"/>
       <c r="K26" s="53"/>
       <c r="O26" s="53"/>
@@ -28608,7 +28672,7 @@
       <c r="BK26" s="53"/>
       <c r="BO26" s="39"/>
     </row>
-    <row r="27" spans="1:67" s="2" customFormat="1" hidden="1">
+    <row r="27" spans="1:67" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="F27" s="53"/>
       <c r="K27" s="53"/>
       <c r="O27" s="53"/>
@@ -28625,7 +28689,7 @@
       <c r="BK27" s="53"/>
       <c r="BO27" s="39"/>
     </row>
-    <row r="28" spans="1:67" s="2" customFormat="1" hidden="1">
+    <row r="28" spans="1:67" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="F28" s="53"/>
       <c r="K28" s="53"/>
       <c r="O28" s="53"/>
@@ -28642,7 +28706,7 @@
       <c r="BK28" s="53"/>
       <c r="BO28" s="39"/>
     </row>
-    <row r="29" spans="1:67" s="2" customFormat="1" hidden="1">
+    <row r="29" spans="1:67" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="F29" s="53"/>
       <c r="K29" s="53"/>
       <c r="O29" s="53"/>
@@ -28659,7 +28723,7 @@
       <c r="BK29" s="53"/>
       <c r="BO29" s="39"/>
     </row>
-    <row r="30" spans="1:67" s="2" customFormat="1">
+    <row r="30" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A30" s="7" t="s">
         <v>46</v>
       </c>
@@ -28730,7 +28794,7 @@
       <c r="BN30" s="6"/>
       <c r="BO30" s="39"/>
     </row>
-    <row r="31" spans="1:67" s="2" customFormat="1">
+    <row r="31" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A31" s="7"/>
       <c r="B31" s="17" t="s">
         <v>64</v>
@@ -28929,7 +28993,7 @@
       </c>
       <c r="BO31" s="39"/>
     </row>
-    <row r="32" spans="1:67" s="2" customFormat="1">
+    <row r="32" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A32" s="11" t="s">
         <v>48</v>
       </c>
@@ -29195,7 +29259,7 @@
       </c>
       <c r="BO32" s="39"/>
     </row>
-    <row r="33" spans="1:67" s="2" customFormat="1">
+    <row r="33" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A33" s="8" t="s">
         <v>49</v>
       </c>
@@ -29461,7 +29525,7 @@
       </c>
       <c r="BO33" s="39"/>
     </row>
-    <row r="34" spans="1:67" s="2" customFormat="1">
+    <row r="34" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A34" s="8" t="s">
         <v>50</v>
       </c>
@@ -29727,7 +29791,7 @@
       </c>
       <c r="BO34" s="39"/>
     </row>
-    <row r="35" spans="1:67" s="2" customFormat="1">
+    <row r="35" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A35" s="8" t="s">
         <v>51</v>
       </c>
@@ -29993,7 +30057,7 @@
       </c>
       <c r="BO35" s="39"/>
     </row>
-    <row r="36" spans="1:67" s="2" customFormat="1">
+    <row r="36" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A36" s="8" t="s">
         <v>52</v>
       </c>
@@ -30259,7 +30323,7 @@
       </c>
       <c r="BO36" s="39"/>
     </row>
-    <row r="37" spans="1:67" s="2" customFormat="1">
+    <row r="37" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A37" s="12"/>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -30328,7 +30392,7 @@
       <c r="BN37" s="6"/>
       <c r="BO37" s="39"/>
     </row>
-    <row r="38" spans="1:67" hidden="1">
+    <row r="38" spans="1:67" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="7" t="s">
         <v>53</v>
       </c>
@@ -30410,7 +30474,7 @@
       <c r="BM38" s="29"/>
       <c r="BN38" s="35"/>
     </row>
-    <row r="39" spans="1:67">
+    <row r="39" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A39" s="8" t="s">
         <v>54</v>
       </c>
@@ -30675,7 +30739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:67">
+    <row r="40" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A40" s="8" t="s">
         <v>55</v>
       </c>
@@ -30940,7 +31004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:67">
+    <row r="41" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A41" s="8" t="s">
         <v>56</v>
       </c>
@@ -31205,7 +31269,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:67">
+    <row r="42" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A42" s="8" t="s">
         <v>57</v>
       </c>
@@ -31470,7 +31534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:67">
+    <row r="43" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A43" s="8" t="s">
         <v>58</v>
       </c>
@@ -31735,7 +31799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:67">
+    <row r="44" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A44" s="8" t="s">
         <v>59</v>
       </c>
@@ -32000,7 +32064,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:67">
+    <row r="45" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A45" s="12"/>
       <c r="B45" s="14"/>
       <c r="C45" s="14"/>
@@ -32068,7 +32132,7 @@
       <c r="BM45" s="14"/>
       <c r="BN45" s="14"/>
     </row>
-    <row r="46" spans="1:67" s="2" customFormat="1">
+    <row r="46" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A46" s="8" t="s">
         <v>31</v>
       </c>
@@ -32334,7 +32398,7 @@
       </c>
       <c r="BO46" s="39"/>
     </row>
-    <row r="47" spans="1:67" s="2" customFormat="1">
+    <row r="47" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A47" s="8" t="s">
         <v>60</v>
       </c>
@@ -32600,7 +32664,7 @@
       </c>
       <c r="BO47" s="39"/>
     </row>
-    <row r="48" spans="1:67" s="2" customFormat="1">
+    <row r="48" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A48" s="8" t="s">
         <v>61</v>
       </c>
@@ -32866,7 +32930,7 @@
       </c>
       <c r="BO48" s="39"/>
     </row>
-    <row r="49" spans="1:67" s="2" customFormat="1">
+    <row r="49" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A49" s="8" t="s">
         <v>62</v>
       </c>
@@ -33132,7 +33196,7 @@
       </c>
       <c r="BO49" s="39"/>
     </row>
-    <row r="50" spans="1:67" s="2" customFormat="1">
+    <row r="50" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A50" s="8" t="s">
         <v>63</v>
       </c>
@@ -33432,15 +33496,15 @@
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:BO56"/>
-  <sheetFormatPr defaultColWidth="10.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="10.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15" style="2" customWidth="1"/>
-    <col min="2" max="66" width="10.7109375" style="2"/>
-    <col min="67" max="67" width="10.7109375" style="39"/>
-    <col min="68" max="16384" width="10.7109375" style="2"/>
+    <col min="2" max="66" width="10.7265625" style="2"/>
+    <col min="67" max="67" width="10.7265625" style="39"/>
+    <col min="68" max="16384" width="10.7265625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:66">
+    <row r="1" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A1" s="9" t="s">
         <v>34</v>
       </c>
@@ -33702,7 +33766,7 @@
         <v>1368</v>
       </c>
     </row>
-    <row r="2" spans="1:66">
+    <row r="2" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
         <v>35</v>
       </c>
@@ -33902,7 +33966,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:66">
+    <row r="3" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>36</v>
       </c>
@@ -34102,7 +34166,7 @@
         <v>46444</v>
       </c>
     </row>
-    <row r="4" spans="1:66">
+    <row r="4" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>37</v>
       </c>
@@ -34172,7 +34236,7 @@
       <c r="BM4" s="6"/>
       <c r="BN4" s="6"/>
     </row>
-    <row r="5" spans="1:66">
+    <row r="5" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
         <v>38</v>
       </c>
@@ -34270,7 +34334,7 @@
       <c r="BM5" s="4"/>
       <c r="BN5" s="4"/>
     </row>
-    <row r="6" spans="1:66">
+    <row r="6" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
         <v>39</v>
       </c>
@@ -34368,7 +34432,7 @@
       <c r="BM6" s="4"/>
       <c r="BN6" s="4"/>
     </row>
-    <row r="7" spans="1:66">
+    <row r="7" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
         <v>40</v>
       </c>
@@ -34466,7 +34530,7 @@
       <c r="BM7" s="4"/>
       <c r="BN7" s="4"/>
     </row>
-    <row r="8" spans="1:66">
+    <row r="8" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
         <v>41</v>
       </c>
@@ -34536,7 +34600,7 @@
       <c r="BM8" s="6"/>
       <c r="BN8" s="6"/>
     </row>
-    <row r="9" spans="1:66">
+    <row r="9" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A9" s="8" t="s">
         <v>38</v>
       </c>
@@ -34634,7 +34698,7 @@
       <c r="BM9" s="4"/>
       <c r="BN9" s="4"/>
     </row>
-    <row r="10" spans="1:66">
+    <row r="10" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
         <v>39</v>
       </c>
@@ -34732,7 +34796,7 @@
       <c r="BM10" s="4"/>
       <c r="BN10" s="4"/>
     </row>
-    <row r="11" spans="1:66">
+    <row r="11" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
         <v>40</v>
       </c>
@@ -34830,7 +34894,7 @@
       <c r="BM11" s="4"/>
       <c r="BN11" s="4"/>
     </row>
-    <row r="12" spans="1:66">
+    <row r="12" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
         <v>42</v>
       </c>
@@ -34900,7 +34964,7 @@
       <c r="BM12" s="7"/>
       <c r="BN12" s="7"/>
     </row>
-    <row r="13" spans="1:66">
+    <row r="13" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A13" s="8" t="s">
         <v>38</v>
       </c>
@@ -34998,7 +35062,7 @@
       <c r="BM13" s="4"/>
       <c r="BN13" s="4"/>
     </row>
-    <row r="14" spans="1:66">
+    <row r="14" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
         <v>39</v>
       </c>
@@ -35096,7 +35160,7 @@
       <c r="BM14" s="4"/>
       <c r="BN14" s="4"/>
     </row>
-    <row r="15" spans="1:66">
+    <row r="15" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A15" s="8" t="s">
         <v>40</v>
       </c>
@@ -35194,7 +35258,7 @@
       <c r="BM15" s="4"/>
       <c r="BN15" s="4"/>
     </row>
-    <row r="16" spans="1:66">
+    <row r="16" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
         <v>43</v>
       </c>
@@ -35264,7 +35328,7 @@
       <c r="BM16" s="7"/>
       <c r="BN16" s="7"/>
     </row>
-    <row r="17" spans="1:66">
+    <row r="17" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A17" s="8" t="s">
         <v>38</v>
       </c>
@@ -35362,7 +35426,7 @@
       <c r="BM17" s="4"/>
       <c r="BN17" s="4"/>
     </row>
-    <row r="18" spans="1:66">
+    <row r="18" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A18" s="8" t="s">
         <v>39</v>
       </c>
@@ -35460,7 +35524,7 @@
       <c r="BM18" s="4"/>
       <c r="BN18" s="4"/>
     </row>
-    <row r="19" spans="1:66">
+    <row r="19" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A19" s="8" t="s">
         <v>40</v>
       </c>
@@ -35558,7 +35622,7 @@
       <c r="BM19" s="4"/>
       <c r="BN19" s="4"/>
     </row>
-    <row r="20" spans="1:66">
+    <row r="20" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A20" s="7" t="s">
         <v>44</v>
       </c>
@@ -35628,7 +35692,7 @@
       <c r="BM20" s="7"/>
       <c r="BN20" s="7"/>
     </row>
-    <row r="21" spans="1:66">
+    <row r="21" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A21" s="8" t="s">
         <v>38</v>
       </c>
@@ -35726,7 +35790,7 @@
       <c r="BM21" s="4"/>
       <c r="BN21" s="4"/>
     </row>
-    <row r="22" spans="1:66">
+    <row r="22" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
         <v>45</v>
       </c>
@@ -35796,7 +35860,7 @@
       <c r="BM22" s="7"/>
       <c r="BN22" s="7"/>
     </row>
-    <row r="23" spans="1:66">
+    <row r="23" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A23" s="8" t="s">
         <v>38</v>
       </c>
@@ -35894,7 +35958,7 @@
       <c r="BM23" s="4"/>
       <c r="BN23" s="4"/>
     </row>
-    <row r="24" spans="1:66">
+    <row r="24" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A24" s="8" t="s">
         <v>39</v>
       </c>
@@ -35992,7 +36056,7 @@
       <c r="BM24" s="4"/>
       <c r="BN24" s="4"/>
     </row>
-    <row r="25" spans="1:66">
+    <row r="25" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A25" s="8" t="s">
         <v>40</v>
       </c>
@@ -36090,7 +36154,7 @@
       <c r="BM25" s="4"/>
       <c r="BN25" s="4"/>
     </row>
-    <row r="26" spans="1:66">
+    <row r="26" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A26" s="6"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -36158,7 +36222,7 @@
       <c r="BM26" s="6"/>
       <c r="BN26" s="6"/>
     </row>
-    <row r="29" spans="1:66">
+    <row r="29" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A29" s="7" t="s">
         <v>46</v>
       </c>
@@ -36228,7 +36292,7 @@
       <c r="BM29" s="6"/>
       <c r="BN29" s="6"/>
     </row>
-    <row r="30" spans="1:66" hidden="1">
+    <row r="30" spans="1:66" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="7" t="s">
         <v>47</v>
       </c>
@@ -36306,7 +36370,7 @@
       <c r="BM30" s="10"/>
       <c r="BN30" s="10"/>
     </row>
-    <row r="31" spans="1:66" hidden="1">
+    <row r="31" spans="1:66" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="8" t="s">
         <v>38</v>
       </c>
@@ -36376,7 +36440,7 @@
       <c r="BM31" s="35"/>
       <c r="BN31" s="35"/>
     </row>
-    <row r="32" spans="1:66" hidden="1">
+    <row r="32" spans="1:66" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="8" t="s">
         <v>39</v>
       </c>
@@ -36446,7 +36510,7 @@
       <c r="BM32" s="35"/>
       <c r="BN32" s="35"/>
     </row>
-    <row r="33" spans="1:66" hidden="1">
+    <row r="33" spans="1:66" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="8" t="s">
         <v>40</v>
       </c>
@@ -36516,7 +36580,7 @@
       <c r="BM33" s="35"/>
       <c r="BN33" s="35"/>
     </row>
-    <row r="34" spans="1:66">
+    <row r="34" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A34" s="7" t="s">
         <v>37</v>
       </c>
@@ -36586,7 +36650,7 @@
       <c r="BM34" s="6"/>
       <c r="BN34" s="6"/>
     </row>
-    <row r="35" spans="1:66">
+    <row r="35" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A35" s="8" t="s">
         <v>38</v>
       </c>
@@ -36851,7 +36915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:66">
+    <row r="36" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A36" s="8" t="s">
         <v>39</v>
       </c>
@@ -37116,7 +37180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:66">
+    <row r="37" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A37" s="8" t="s">
         <v>40</v>
       </c>
@@ -37381,7 +37445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:66">
+    <row r="38" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A38" s="7" t="s">
         <v>41</v>
       </c>
@@ -37451,7 +37515,7 @@
       <c r="BM38" s="6"/>
       <c r="BN38" s="6"/>
     </row>
-    <row r="39" spans="1:66">
+    <row r="39" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A39" s="8" t="s">
         <v>38</v>
       </c>
@@ -37716,7 +37780,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:66">
+    <row r="40" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A40" s="8" t="s">
         <v>39</v>
       </c>
@@ -37981,7 +38045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:66">
+    <row r="41" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A41" s="8" t="s">
         <v>40</v>
       </c>
@@ -38246,7 +38310,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:66">
+    <row r="42" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A42" s="7" t="s">
         <v>42</v>
       </c>
@@ -38316,7 +38380,7 @@
       <c r="BM42" s="6"/>
       <c r="BN42" s="6"/>
     </row>
-    <row r="43" spans="1:66">
+    <row r="43" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A43" s="8" t="s">
         <v>38</v>
       </c>
@@ -38581,7 +38645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:66">
+    <row r="44" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A44" s="8" t="s">
         <v>39</v>
       </c>
@@ -38846,7 +38910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:66">
+    <row r="45" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A45" s="8" t="s">
         <v>40</v>
       </c>
@@ -39111,7 +39175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:66">
+    <row r="46" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A46" s="7" t="s">
         <v>43</v>
       </c>
@@ -39181,7 +39245,7 @@
       <c r="BM46" s="6"/>
       <c r="BN46" s="6"/>
     </row>
-    <row r="47" spans="1:66">
+    <row r="47" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A47" s="8" t="s">
         <v>38</v>
       </c>
@@ -39446,7 +39510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:66">
+    <row r="48" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A48" s="8" t="s">
         <v>39</v>
       </c>
@@ -39711,7 +39775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:66">
+    <row r="49" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A49" s="8" t="s">
         <v>40</v>
       </c>
@@ -39976,7 +40040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:66">
+    <row r="50" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A50" s="7" t="s">
         <v>44</v>
       </c>
@@ -40046,7 +40110,7 @@
       <c r="BM50" s="6"/>
       <c r="BN50" s="6"/>
     </row>
-    <row r="51" spans="1:66">
+    <row r="51" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A51" s="8" t="s">
         <v>38</v>
       </c>
@@ -40311,7 +40375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:66">
+    <row r="52" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A52" s="7" t="s">
         <v>45</v>
       </c>
@@ -40381,7 +40445,7 @@
       <c r="BM52" s="6"/>
       <c r="BN52" s="6"/>
     </row>
-    <row r="53" spans="1:66">
+    <row r="53" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A53" s="8" t="s">
         <v>38</v>
       </c>
@@ -40646,7 +40710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:66">
+    <row r="54" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A54" s="8" t="s">
         <v>39</v>
       </c>
@@ -40911,7 +40975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:66">
+    <row r="55" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A55" s="8" t="s">
         <v>40</v>
       </c>
@@ -41176,7 +41240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:66">
+    <row r="56" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A56" s="6"/>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
@@ -41340,13 +41404,13 @@
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:BO50"/>
-  <sheetFormatPr defaultColWidth="12.140625" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="12.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="31.28515625" customWidth="1"/>
-    <col min="67" max="67" width="12.140625" style="41"/>
+    <col min="1" max="1" width="31.26953125" customWidth="1"/>
+    <col min="67" max="67" width="12.1796875" style="41"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:67" s="2" customFormat="1">
+    <row r="1" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="9" t="s">
         <v>34</v>
       </c>
@@ -41609,7 +41673,7 @@
       </c>
       <c r="BO1" s="39"/>
     </row>
-    <row r="2" spans="1:67" s="2" customFormat="1">
+    <row r="2" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
         <v>35</v>
       </c>
@@ -41810,7 +41874,7 @@
       </c>
       <c r="BO2" s="39"/>
     </row>
-    <row r="3" spans="1:67" s="2" customFormat="1">
+    <row r="3" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>36</v>
       </c>
@@ -42011,7 +42075,7 @@
       </c>
       <c r="BO3" s="39"/>
     </row>
-    <row r="4" spans="1:67" s="2" customFormat="1">
+    <row r="4" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="11" t="s">
         <v>48</v>
       </c>
@@ -42114,7 +42178,7 @@
       <c r="BN4" s="4"/>
       <c r="BO4" s="39"/>
     </row>
-    <row r="5" spans="1:67" s="2" customFormat="1">
+    <row r="5" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
         <v>49</v>
       </c>
@@ -42213,7 +42277,7 @@
       <c r="BN5" s="4"/>
       <c r="BO5" s="39"/>
     </row>
-    <row r="6" spans="1:67" s="2" customFormat="1">
+    <row r="6" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
         <v>50</v>
       </c>
@@ -42312,7 +42376,7 @@
       <c r="BN6" s="4"/>
       <c r="BO6" s="39"/>
     </row>
-    <row r="7" spans="1:67" s="2" customFormat="1">
+    <row r="7" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
         <v>51</v>
       </c>
@@ -42411,7 +42475,7 @@
       <c r="BN7" s="4"/>
       <c r="BO7" s="39"/>
     </row>
-    <row r="8" spans="1:67" s="2" customFormat="1">
+    <row r="8" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="8" t="s">
         <v>52</v>
       </c>
@@ -42510,7 +42574,7 @@
       <c r="BN8" s="4"/>
       <c r="BO8" s="39"/>
     </row>
-    <row r="9" spans="1:67" s="2" customFormat="1">
+    <row r="9" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A9" s="12"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -42579,7 +42643,7 @@
       <c r="BN9" s="6"/>
       <c r="BO9" s="39"/>
     </row>
-    <row r="10" spans="1:67" hidden="1">
+    <row r="10" spans="1:67" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
         <v>53</v>
       </c>
@@ -42649,7 +42713,7 @@
       <c r="BM10" s="4"/>
       <c r="BN10" s="4"/>
     </row>
-    <row r="11" spans="1:67">
+    <row r="11" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
         <v>54</v>
       </c>
@@ -42747,7 +42811,7 @@
       <c r="BM11" s="4"/>
       <c r="BN11" s="4"/>
     </row>
-    <row r="12" spans="1:67">
+    <row r="12" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A12" s="8" t="s">
         <v>55</v>
       </c>
@@ -42845,7 +42909,7 @@
       <c r="BM12" s="4"/>
       <c r="BN12" s="4"/>
     </row>
-    <row r="13" spans="1:67">
+    <row r="13" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A13" s="8" t="s">
         <v>56</v>
       </c>
@@ -42943,7 +43007,7 @@
       <c r="BM13" s="4"/>
       <c r="BN13" s="4"/>
     </row>
-    <row r="14" spans="1:67">
+    <row r="14" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
         <v>57</v>
       </c>
@@ -43041,7 +43105,7 @@
       <c r="BM14" s="4"/>
       <c r="BN14" s="4"/>
     </row>
-    <row r="15" spans="1:67">
+    <row r="15" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A15" s="8" t="s">
         <v>58</v>
       </c>
@@ -43139,7 +43203,7 @@
       <c r="BM15" s="4"/>
       <c r="BN15" s="4"/>
     </row>
-    <row r="16" spans="1:67">
+    <row r="16" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A16" s="8" t="s">
         <v>59</v>
       </c>
@@ -43237,7 +43301,7 @@
       <c r="BM16" s="4"/>
       <c r="BN16" s="4"/>
     </row>
-    <row r="17" spans="1:67">
+    <row r="17" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A17" s="12"/>
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
@@ -43305,7 +43369,7 @@
       <c r="BM17" s="14"/>
       <c r="BN17" s="14"/>
     </row>
-    <row r="18" spans="1:67" s="2" customFormat="1">
+    <row r="18" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A18" s="8" t="s">
         <v>31</v>
       </c>
@@ -43404,7 +43468,7 @@
       <c r="BN18" s="4"/>
       <c r="BO18" s="39"/>
     </row>
-    <row r="19" spans="1:67" s="2" customFormat="1">
+    <row r="19" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A19" s="8" t="s">
         <v>60</v>
       </c>
@@ -43503,7 +43567,7 @@
       <c r="BN19" s="4"/>
       <c r="BO19" s="39"/>
     </row>
-    <row r="20" spans="1:67" s="2" customFormat="1">
+    <row r="20" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A20" s="8" t="s">
         <v>61</v>
       </c>
@@ -43602,7 +43666,7 @@
       <c r="BN20" s="4"/>
       <c r="BO20" s="39"/>
     </row>
-    <row r="21" spans="1:67" s="2" customFormat="1">
+    <row r="21" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A21" s="8" t="s">
         <v>62</v>
       </c>
@@ -43701,7 +43765,7 @@
       <c r="BN21" s="4"/>
       <c r="BO21" s="39"/>
     </row>
-    <row r="22" spans="1:67" s="2" customFormat="1">
+    <row r="22" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
         <v>63</v>
       </c>
@@ -43800,7 +43864,7 @@
       <c r="BN22" s="4"/>
       <c r="BO22" s="39"/>
     </row>
-    <row r="23" spans="1:67" s="2" customFormat="1">
+    <row r="23" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A23" s="6"/>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
@@ -43869,25 +43933,25 @@
       <c r="BN23" s="6"/>
       <c r="BO23" s="39"/>
     </row>
-    <row r="24" spans="1:67" s="2" customFormat="1">
+    <row r="24" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="BO24" s="39"/>
     </row>
-    <row r="25" spans="1:67" s="2" customFormat="1">
+    <row r="25" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="BO25" s="39"/>
     </row>
-    <row r="26" spans="1:67" s="2" customFormat="1" hidden="1">
+    <row r="26" spans="1:67" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="BO26" s="39"/>
     </row>
-    <row r="27" spans="1:67" s="2" customFormat="1" hidden="1">
+    <row r="27" spans="1:67" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="BO27" s="39"/>
     </row>
-    <row r="28" spans="1:67" s="2" customFormat="1" hidden="1">
+    <row r="28" spans="1:67" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="BO28" s="39"/>
     </row>
-    <row r="29" spans="1:67" s="2" customFormat="1" hidden="1">
+    <row r="29" spans="1:67" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="BO29" s="39"/>
     </row>
-    <row r="30" spans="1:67" s="2" customFormat="1">
+    <row r="30" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A30" s="7" t="s">
         <v>46</v>
       </c>
@@ -43958,7 +44022,7 @@
       <c r="BN30" s="6"/>
       <c r="BO30" s="39"/>
     </row>
-    <row r="31" spans="1:67" s="2" customFormat="1">
+    <row r="31" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A31" s="7"/>
       <c r="B31" s="17" t="s">
         <v>64</v>
@@ -44157,7 +44221,7 @@
       </c>
       <c r="BO31" s="39"/>
     </row>
-    <row r="32" spans="1:67" s="2" customFormat="1">
+    <row r="32" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A32" s="11" t="s">
         <v>48</v>
       </c>
@@ -44423,7 +44487,7 @@
       </c>
       <c r="BO32" s="39"/>
     </row>
-    <row r="33" spans="1:67" s="2" customFormat="1">
+    <row r="33" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A33" s="8" t="s">
         <v>49</v>
       </c>
@@ -44689,7 +44753,7 @@
       </c>
       <c r="BO33" s="39"/>
     </row>
-    <row r="34" spans="1:67" s="2" customFormat="1">
+    <row r="34" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A34" s="8" t="s">
         <v>50</v>
       </c>
@@ -44955,7 +45019,7 @@
       </c>
       <c r="BO34" s="39"/>
     </row>
-    <row r="35" spans="1:67" s="2" customFormat="1">
+    <row r="35" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A35" s="8" t="s">
         <v>51</v>
       </c>
@@ -45221,7 +45285,7 @@
       </c>
       <c r="BO35" s="39"/>
     </row>
-    <row r="36" spans="1:67" s="2" customFormat="1">
+    <row r="36" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A36" s="8" t="s">
         <v>52</v>
       </c>
@@ -45487,7 +45551,7 @@
       </c>
       <c r="BO36" s="39"/>
     </row>
-    <row r="37" spans="1:67" s="2" customFormat="1">
+    <row r="37" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A37" s="12"/>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -45556,7 +45620,7 @@
       <c r="BN37" s="6"/>
       <c r="BO37" s="39"/>
     </row>
-    <row r="38" spans="1:67">
+    <row r="38" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A38" s="7" t="s">
         <v>53</v>
       </c>
@@ -45821,7 +45885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:67">
+    <row r="39" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A39" s="8" t="s">
         <v>54</v>
       </c>
@@ -46086,7 +46150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:67">
+    <row r="40" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A40" s="8" t="s">
         <v>55</v>
       </c>
@@ -46351,7 +46415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:67">
+    <row r="41" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A41" s="8" t="s">
         <v>56</v>
       </c>
@@ -46616,7 +46680,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:67">
+    <row r="42" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A42" s="8" t="s">
         <v>57</v>
       </c>
@@ -46881,7 +46945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:67">
+    <row r="43" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A43" s="8" t="s">
         <v>58</v>
       </c>
@@ -47146,7 +47210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:67">
+    <row r="44" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A44" s="8" t="s">
         <v>59</v>
       </c>
@@ -47411,7 +47475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:67">
+    <row r="45" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A45" s="12"/>
       <c r="B45" s="14"/>
       <c r="C45" s="14"/>
@@ -47479,7 +47543,7 @@
       <c r="BM45" s="14"/>
       <c r="BN45" s="14"/>
     </row>
-    <row r="46" spans="1:67" s="2" customFormat="1">
+    <row r="46" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A46" s="8" t="s">
         <v>31</v>
       </c>
@@ -47745,7 +47809,7 @@
       </c>
       <c r="BO46" s="39"/>
     </row>
-    <row r="47" spans="1:67" s="2" customFormat="1">
+    <row r="47" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A47" s="8" t="s">
         <v>60</v>
       </c>
@@ -48011,7 +48075,7 @@
       </c>
       <c r="BO47" s="39"/>
     </row>
-    <row r="48" spans="1:67" s="2" customFormat="1">
+    <row r="48" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A48" s="8" t="s">
         <v>61</v>
       </c>
@@ -48277,7 +48341,7 @@
       </c>
       <c r="BO48" s="39"/>
     </row>
-    <row r="49" spans="1:67" s="2" customFormat="1">
+    <row r="49" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A49" s="8" t="s">
         <v>62</v>
       </c>
@@ -48543,7 +48607,7 @@
       </c>
       <c r="BO49" s="39"/>
     </row>
-    <row r="50" spans="1:67" s="2" customFormat="1">
+    <row r="50" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A50" s="8" t="s">
         <v>63</v>
       </c>
@@ -48909,15 +48973,15 @@
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:BO64"/>
-  <sheetFormatPr defaultColWidth="10.5703125" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="10.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" style="2" customWidth="1"/>
-    <col min="2" max="66" width="10.5703125" style="2"/>
-    <col min="67" max="67" width="10.5703125" style="39"/>
-    <col min="68" max="16384" width="10.5703125" style="2"/>
+    <col min="1" max="1" width="12.81640625" style="2" customWidth="1"/>
+    <col min="2" max="66" width="10.54296875" style="2"/>
+    <col min="67" max="67" width="10.54296875" style="39"/>
+    <col min="68" max="16384" width="10.54296875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:66">
+    <row r="1" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A1" s="9" t="s">
         <v>34</v>
       </c>
@@ -49117,7 +49181,7 @@
         <v>8760</v>
       </c>
     </row>
-    <row r="2" spans="1:66">
+    <row r="2" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
         <v>35</v>
       </c>
@@ -49317,7 +49381,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:66">
+    <row r="3" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>36</v>
       </c>
@@ -49517,7 +49581,7 @@
         <v>46444</v>
       </c>
     </row>
-    <row r="4" spans="1:66">
+    <row r="4" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>37</v>
       </c>
@@ -49587,7 +49651,7 @@
       <c r="BM4" s="6"/>
       <c r="BN4" s="6"/>
     </row>
-    <row r="5" spans="1:66">
+    <row r="5" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
         <v>38</v>
       </c>
@@ -49699,7 +49763,7 @@
       <c r="BM5" s="4"/>
       <c r="BN5" s="4"/>
     </row>
-    <row r="6" spans="1:66">
+    <row r="6" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
         <v>39</v>
       </c>
@@ -49797,7 +49861,7 @@
       <c r="BM6" s="4"/>
       <c r="BN6" s="4"/>
     </row>
-    <row r="7" spans="1:66">
+    <row r="7" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
         <v>40</v>
       </c>
@@ -49895,7 +49959,7 @@
       <c r="BM7" s="4"/>
       <c r="BN7" s="4"/>
     </row>
-    <row r="8" spans="1:66">
+    <row r="8" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
         <v>41</v>
       </c>
@@ -49965,7 +50029,7 @@
       <c r="BM8" s="6"/>
       <c r="BN8" s="6"/>
     </row>
-    <row r="9" spans="1:66">
+    <row r="9" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A9" s="8" t="s">
         <v>38</v>
       </c>
@@ -50063,7 +50127,7 @@
       <c r="BM9" s="4"/>
       <c r="BN9" s="4"/>
     </row>
-    <row r="10" spans="1:66">
+    <row r="10" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
         <v>39</v>
       </c>
@@ -50161,7 +50225,7 @@
       <c r="BM10" s="4"/>
       <c r="BN10" s="4"/>
     </row>
-    <row r="11" spans="1:66">
+    <row r="11" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
         <v>40</v>
       </c>
@@ -50259,7 +50323,7 @@
       <c r="BM11" s="4"/>
       <c r="BN11" s="4"/>
     </row>
-    <row r="12" spans="1:66">
+    <row r="12" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
         <v>42</v>
       </c>
@@ -50329,7 +50393,7 @@
       <c r="BM12" s="7"/>
       <c r="BN12" s="7"/>
     </row>
-    <row r="13" spans="1:66">
+    <row r="13" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A13" s="8" t="s">
         <v>38</v>
       </c>
@@ -50427,7 +50491,7 @@
       <c r="BM13" s="4"/>
       <c r="BN13" s="4"/>
     </row>
-    <row r="14" spans="1:66">
+    <row r="14" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
         <v>39</v>
       </c>
@@ -50525,7 +50589,7 @@
       <c r="BM14" s="4"/>
       <c r="BN14" s="4"/>
     </row>
-    <row r="15" spans="1:66">
+    <row r="15" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A15" s="8" t="s">
         <v>40</v>
       </c>
@@ -50623,7 +50687,7 @@
       <c r="BM15" s="4"/>
       <c r="BN15" s="4"/>
     </row>
-    <row r="16" spans="1:66">
+    <row r="16" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
         <v>43</v>
       </c>
@@ -50693,7 +50757,7 @@
       <c r="BM16" s="7"/>
       <c r="BN16" s="7"/>
     </row>
-    <row r="17" spans="1:66">
+    <row r="17" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A17" s="8" t="s">
         <v>38</v>
       </c>
@@ -50791,7 +50855,7 @@
       <c r="BM17" s="4"/>
       <c r="BN17" s="4"/>
     </row>
-    <row r="18" spans="1:66">
+    <row r="18" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A18" s="8" t="s">
         <v>39</v>
       </c>
@@ -50889,7 +50953,7 @@
       <c r="BM18" s="4"/>
       <c r="BN18" s="4"/>
     </row>
-    <row r="19" spans="1:66">
+    <row r="19" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A19" s="8" t="s">
         <v>40</v>
       </c>
@@ -50987,7 +51051,7 @@
       <c r="BM19" s="4"/>
       <c r="BN19" s="4"/>
     </row>
-    <row r="20" spans="1:66">
+    <row r="20" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A20" s="7" t="s">
         <v>44</v>
       </c>
@@ -51057,7 +51121,7 @@
       <c r="BM20" s="7"/>
       <c r="BN20" s="7"/>
     </row>
-    <row r="21" spans="1:66">
+    <row r="21" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A21" s="8" t="s">
         <v>38</v>
       </c>
@@ -51155,7 +51219,7 @@
       <c r="BM21" s="4"/>
       <c r="BN21" s="4"/>
     </row>
-    <row r="22" spans="1:66">
+    <row r="22" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
         <v>45</v>
       </c>
@@ -51225,7 +51289,7 @@
       <c r="BM22" s="7"/>
       <c r="BN22" s="7"/>
     </row>
-    <row r="23" spans="1:66">
+    <row r="23" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A23" s="8" t="s">
         <v>38</v>
       </c>
@@ -51323,7 +51387,7 @@
       <c r="BM23" s="4"/>
       <c r="BN23" s="4"/>
     </row>
-    <row r="24" spans="1:66">
+    <row r="24" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A24" s="8" t="s">
         <v>39</v>
       </c>
@@ -51421,7 +51485,7 @@
       <c r="BM24" s="4"/>
       <c r="BN24" s="4"/>
     </row>
-    <row r="25" spans="1:66">
+    <row r="25" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A25" s="8" t="s">
         <v>40</v>
       </c>
@@ -51519,7 +51583,7 @@
       <c r="BM25" s="4"/>
       <c r="BN25" s="4"/>
     </row>
-    <row r="26" spans="1:66">
+    <row r="26" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A26" s="6"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -51587,7 +51651,7 @@
       <c r="BM26" s="6"/>
       <c r="BN26" s="6"/>
     </row>
-    <row r="29" spans="1:66">
+    <row r="29" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A29" s="7" t="s">
         <v>46</v>
       </c>
@@ -51657,7 +51721,7 @@
       <c r="BM29" s="6"/>
       <c r="BN29" s="6"/>
     </row>
-    <row r="30" spans="1:66">
+    <row r="30" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A30" s="7" t="s">
         <v>47</v>
       </c>
@@ -51727,7 +51791,7 @@
       <c r="BM30" s="6"/>
       <c r="BN30" s="6"/>
     </row>
-    <row r="31" spans="1:66" hidden="1">
+    <row r="31" spans="1:66" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="8" t="s">
         <v>38</v>
       </c>
@@ -51809,7 +51873,7 @@
       <c r="BM31" s="5"/>
       <c r="BN31" s="5"/>
     </row>
-    <row r="32" spans="1:66" hidden="1">
+    <row r="32" spans="1:66" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="8" t="s">
         <v>39</v>
       </c>
@@ -51891,7 +51955,7 @@
       <c r="BM32" s="5"/>
       <c r="BN32" s="5"/>
     </row>
-    <row r="33" spans="1:66" hidden="1">
+    <row r="33" spans="1:66" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="8" t="s">
         <v>40</v>
       </c>
@@ -51973,7 +52037,7 @@
       <c r="BM33" s="5"/>
       <c r="BN33" s="5"/>
     </row>
-    <row r="34" spans="1:66">
+    <row r="34" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A34" s="7" t="s">
         <v>37</v>
       </c>
@@ -52043,7 +52107,7 @@
       <c r="BM34" s="6"/>
       <c r="BN34" s="6"/>
     </row>
-    <row r="35" spans="1:66">
+    <row r="35" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A35" s="8" t="s">
         <v>38</v>
       </c>
@@ -52308,7 +52372,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:66">
+    <row r="36" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A36" s="8" t="s">
         <v>39</v>
       </c>
@@ -52573,7 +52637,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:66">
+    <row r="37" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A37" s="8" t="s">
         <v>40</v>
       </c>
@@ -52838,7 +52902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:66">
+    <row r="38" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A38" s="7" t="s">
         <v>41</v>
       </c>
@@ -52908,7 +52972,7 @@
       <c r="BM38" s="6"/>
       <c r="BN38" s="6"/>
     </row>
-    <row r="39" spans="1:66">
+    <row r="39" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A39" s="8" t="s">
         <v>38</v>
       </c>
@@ -53173,7 +53237,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:66">
+    <row r="40" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A40" s="8" t="s">
         <v>39</v>
       </c>
@@ -53438,7 +53502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:66">
+    <row r="41" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A41" s="8" t="s">
         <v>40</v>
       </c>
@@ -53703,7 +53767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:66">
+    <row r="42" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A42" s="7" t="s">
         <v>42</v>
       </c>
@@ -53773,7 +53837,7 @@
       <c r="BM42" s="6"/>
       <c r="BN42" s="6"/>
     </row>
-    <row r="43" spans="1:66">
+    <row r="43" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A43" s="8" t="s">
         <v>38</v>
       </c>
@@ -54038,7 +54102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:66">
+    <row r="44" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A44" s="8" t="s">
         <v>39</v>
       </c>
@@ -54303,7 +54367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:66">
+    <row r="45" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A45" s="8" t="s">
         <v>40</v>
       </c>
@@ -54568,7 +54632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:66">
+    <row r="46" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A46" s="7" t="s">
         <v>43</v>
       </c>
@@ -54638,7 +54702,7 @@
       <c r="BM46" s="6"/>
       <c r="BN46" s="6"/>
     </row>
-    <row r="47" spans="1:66">
+    <row r="47" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A47" s="8" t="s">
         <v>38</v>
       </c>
@@ -54903,7 +54967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:66">
+    <row r="48" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A48" s="8" t="s">
         <v>39</v>
       </c>
@@ -55168,7 +55232,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:66">
+    <row r="49" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A49" s="8" t="s">
         <v>40</v>
       </c>
@@ -55433,7 +55497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:66">
+    <row r="50" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A50" s="7" t="s">
         <v>44</v>
       </c>
@@ -55503,7 +55567,7 @@
       <c r="BM50" s="6"/>
       <c r="BN50" s="6"/>
     </row>
-    <row r="51" spans="1:66">
+    <row r="51" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A51" s="8" t="s">
         <v>38</v>
       </c>
@@ -55768,7 +55832,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:66">
+    <row r="52" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A52" s="7" t="s">
         <v>45</v>
       </c>
@@ -55838,7 +55902,7 @@
       <c r="BM52" s="6"/>
       <c r="BN52" s="6"/>
     </row>
-    <row r="53" spans="1:66">
+    <row r="53" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A53" s="8" t="s">
         <v>38</v>
       </c>
@@ -56103,7 +56167,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:66">
+    <row r="54" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A54" s="8" t="s">
         <v>39</v>
       </c>
@@ -56368,7 +56432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:66">
+    <row r="55" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A55" s="8" t="s">
         <v>40</v>
       </c>
@@ -56633,7 +56697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:66">
+    <row r="56" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A56" s="6"/>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
@@ -56701,32 +56765,32 @@
       <c r="BM56" s="6"/>
       <c r="BN56" s="6"/>
     </row>
-    <row r="58" spans="1:66">
+    <row r="58" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A58" s="13" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="60" spans="1:66">
+    <row r="60" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A60" s="24" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="61" spans="1:66">
+    <row r="61" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A61" s="24" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="62" spans="1:66">
+    <row r="62" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="63" spans="1:66">
+    <row r="63" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="64" spans="1:66">
+    <row r="64" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A64" s="24" t="s">
         <v>73</v>
       </c>
@@ -56782,15 +56846,15 @@
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:BO43"/>
-  <sheetFormatPr defaultColWidth="12.140625" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="12.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="31.5703125" style="2" customWidth="1"/>
-    <col min="2" max="66" width="12.140625" style="2"/>
-    <col min="67" max="67" width="12.140625" style="39"/>
-    <col min="68" max="16384" width="12.140625" style="2"/>
+    <col min="1" max="1" width="31.54296875" style="2" customWidth="1"/>
+    <col min="2" max="66" width="12.1796875" style="2"/>
+    <col min="67" max="67" width="12.1796875" style="39"/>
+    <col min="68" max="16384" width="12.1796875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:66">
+    <row r="1" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A1" s="9" t="s">
         <v>34</v>
       </c>
@@ -56990,7 +57054,7 @@
         <v>8760</v>
       </c>
     </row>
-    <row r="2" spans="1:66">
+    <row r="2" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
         <v>35</v>
       </c>
@@ -57190,7 +57254,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:66">
+    <row r="3" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>36</v>
       </c>
@@ -57390,7 +57454,7 @@
         <v>46444</v>
       </c>
     </row>
-    <row r="4" spans="1:66">
+    <row r="4" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A4" s="11" t="s">
         <v>48</v>
       </c>
@@ -57502,7 +57566,7 @@
       <c r="BM4" s="4"/>
       <c r="BN4" s="4"/>
     </row>
-    <row r="5" spans="1:66">
+    <row r="5" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
         <v>49</v>
       </c>
@@ -57600,7 +57664,7 @@
       <c r="BM5" s="4"/>
       <c r="BN5" s="4"/>
     </row>
-    <row r="6" spans="1:66">
+    <row r="6" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
         <v>50</v>
       </c>
@@ -57700,7 +57764,7 @@
       <c r="BM6" s="4"/>
       <c r="BN6" s="4"/>
     </row>
-    <row r="7" spans="1:66">
+    <row r="7" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
         <v>51</v>
       </c>
@@ -57798,7 +57862,7 @@
       <c r="BM7" s="4"/>
       <c r="BN7" s="4"/>
     </row>
-    <row r="8" spans="1:66">
+    <row r="8" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A8" s="8" t="s">
         <v>52</v>
       </c>
@@ -57896,7 +57960,7 @@
       <c r="BM8" s="4"/>
       <c r="BN8" s="4"/>
     </row>
-    <row r="9" spans="1:66">
+    <row r="9" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A9" s="12"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -57964,7 +58028,7 @@
       <c r="BM9" s="6"/>
       <c r="BN9" s="6"/>
     </row>
-    <row r="10" spans="1:66">
+    <row r="10" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
         <v>31</v>
       </c>
@@ -58064,7 +58128,7 @@
       <c r="BM10" s="4"/>
       <c r="BN10" s="4"/>
     </row>
-    <row r="11" spans="1:66">
+    <row r="11" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
         <v>60</v>
       </c>
@@ -58164,7 +58228,7 @@
       <c r="BM11" s="4"/>
       <c r="BN11" s="4"/>
     </row>
-    <row r="12" spans="1:66">
+    <row r="12" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A12" s="8" t="s">
         <v>61</v>
       </c>
@@ -58262,7 +58326,7 @@
       <c r="BM12" s="4"/>
       <c r="BN12" s="4"/>
     </row>
-    <row r="13" spans="1:66">
+    <row r="13" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A13" s="8" t="s">
         <v>62</v>
       </c>
@@ -58362,7 +58426,7 @@
       <c r="BM13" s="4"/>
       <c r="BN13" s="4"/>
     </row>
-    <row r="14" spans="1:66">
+    <row r="14" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
         <v>63</v>
       </c>
@@ -58462,7 +58526,7 @@
       <c r="BM14" s="4"/>
       <c r="BN14" s="4"/>
     </row>
-    <row r="15" spans="1:66">
+    <row r="15" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
@@ -58530,11 +58594,11 @@
       <c r="BM15" s="6"/>
       <c r="BN15" s="6"/>
     </row>
-    <row r="18" spans="1:66" hidden="1"/>
-    <row r="19" spans="1:66" hidden="1"/>
-    <row r="20" spans="1:66" hidden="1"/>
-    <row r="21" spans="1:66" hidden="1"/>
-    <row r="22" spans="1:66">
+    <row r="18" spans="1:66" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="19" spans="1:66" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="1:66" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="21" spans="1:66" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="22" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
         <v>46</v>
       </c>
@@ -58604,7 +58668,7 @@
       <c r="BM22" s="6"/>
       <c r="BN22" s="6"/>
     </row>
-    <row r="23" spans="1:66">
+    <row r="23" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A23" s="7"/>
       <c r="B23" s="10">
         <v>49</v>
@@ -58802,7 +58866,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:66">
+    <row r="24" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A24" s="11" t="s">
         <v>48</v>
       </c>
@@ -59067,7 +59131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:66">
+    <row r="25" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A25" s="8" t="s">
         <v>49</v>
       </c>
@@ -59332,7 +59396,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:66">
+    <row r="26" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A26" s="8" t="s">
         <v>50</v>
       </c>
@@ -59597,7 +59661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:66">
+    <row r="27" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A27" s="8" t="s">
         <v>51</v>
       </c>
@@ -59862,7 +59926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:66">
+    <row r="28" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A28" s="8" t="s">
         <v>52</v>
       </c>
@@ -60127,7 +60191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:66">
+    <row r="29" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A29" s="12"/>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
@@ -60195,7 +60259,7 @@
       <c r="BM29" s="6"/>
       <c r="BN29" s="6"/>
     </row>
-    <row r="30" spans="1:66">
+    <row r="30" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A30" s="8" t="s">
         <v>31</v>
       </c>
@@ -60460,7 +60524,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:66">
+    <row r="31" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A31" s="8" t="s">
         <v>60</v>
       </c>
@@ -60725,7 +60789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:66">
+    <row r="32" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A32" s="8" t="s">
         <v>61</v>
       </c>
@@ -60990,7 +61054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:66">
+    <row r="33" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A33" s="8" t="s">
         <v>62</v>
       </c>
@@ -61255,7 +61319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:66">
+    <row r="34" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A34" s="8" t="s">
         <v>63</v>
       </c>
@@ -61520,32 +61584,32 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:66">
+    <row r="36" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="39" spans="1:66">
+    <row r="39" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A39" s="24" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="40" spans="1:66">
+    <row r="40" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A40" s="24" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="41" spans="1:66">
+    <row r="41" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A41" s="24" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="42" spans="1:66">
+    <row r="42" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A42" s="24" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="43" spans="1:66">
+    <row r="43" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A43" s="24" t="s">
         <v>73</v>
       </c>
@@ -61618,23 +61682,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="07fd80ce-3c18-45d8-8834-03c09a36cfb3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3610c760-99f3-4c2b-a9e3-774f813ef515">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_Flow_SignoffStatus xmlns="3610c760-99f3-4c2b-a9e3-774f813ef515" xsi:nil="true"/>
-    <SharedWithUsers xmlns="7853f155-2f45-42f9-be0e-7ced2fb84d2e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <MediaLengthInSeconds xmlns="3610c760-99f3-4c2b-a9e3-774f813ef515" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -61878,22 +61931,61 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="07fd80ce-3c18-45d8-8834-03c09a36cfb3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3610c760-99f3-4c2b-a9e3-774f813ef515">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_Flow_SignoffStatus xmlns="3610c760-99f3-4c2b-a9e3-774f813ef515" xsi:nil="true"/>
+    <SharedWithUsers xmlns="7853f155-2f45-42f9-be0e-7ced2fb84d2e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <MediaLengthInSeconds xmlns="3610c760-99f3-4c2b-a9e3-774f813ef515" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{319254B0-CD87-430E-84EB-EB503BED7AE2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1C5FC5C-B02A-4EC1-82E7-9682C4BC10F6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AB95B7F-1893-4F31-94E0-BA19E49F8A99}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AB95B7F-1893-4F31-94E0-BA19E49F8A99}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3610c760-99f3-4c2b-a9e3-774f813ef515"/>
+    <ds:schemaRef ds:uri="7853f155-2f45-42f9-be0e-7ced2fb84d2e"/>
+    <ds:schemaRef ds:uri="07fd80ce-3c18-45d8-8834-03c09a36cfb3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1C5FC5C-B02A-4EC1-82E7-9682C4BC10F6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{319254B0-CD87-430E-84EB-EB503BED7AE2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="07fd80ce-3c18-45d8-8834-03c09a36cfb3"/>
+    <ds:schemaRef ds:uri="3610c760-99f3-4c2b-a9e3-774f813ef515"/>
+    <ds:schemaRef ds:uri="7853f155-2f45-42f9-be0e-7ced2fb84d2e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>